--- a/research/traditional_assets/database/data/south_korea/south_korea_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_retail_building_supply.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09334604328184642</v>
+        <v>0.09314642817364181</v>
       </c>
       <c r="C2">
-        <v>42.43334227588386</v>
+        <v>42.12871735598424</v>
       </c>
       <c r="D2">
-        <v>41.87534227588386</v>
+        <v>42.01971735598424</v>
       </c>
       <c r="E2">
-        <v>-13.6</v>
+        <v>-13.151</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.449</v>
       </c>
       <c r="G2">
         <v>0.5580000000000001</v>
@@ -1439,28 +1439,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0225847</v>
       </c>
       <c r="N2">
-        <v>2.880000000000001</v>
+        <v>2.857415300000001</v>
       </c>
       <c r="O2">
-        <v>0.7200000000000002</v>
+        <v>0.7143538250000002</v>
       </c>
       <c r="P2">
-        <v>2.160000000000001</v>
+        <v>2.143061475000001</v>
       </c>
       <c r="Q2">
-        <v>4.130000000000001</v>
+        <v>4.113061475</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09334604328184642</v>
+        <v>0.09370624057943618</v>
       </c>
       <c r="T2">
-        <v>0.952996724804112</v>
+        <v>0.9602163969617189</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>127.5199582017915</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09314642817364181</v>
+        <v>0.0929468130654372</v>
       </c>
       <c r="C3">
-        <v>42.12871735598424</v>
+        <v>41.82509141430894</v>
       </c>
       <c r="D3">
-        <v>42.01971735598424</v>
+        <v>42.16509141430894</v>
       </c>
       <c r="E3">
-        <v>-13.151</v>
+        <v>-12.702</v>
       </c>
       <c r="F3">
-        <v>0.449</v>
+        <v>0.898</v>
       </c>
       <c r="G3">
         <v>0.5580000000000001</v>
@@ -1521,28 +1521,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0225847</v>
+        <v>0.0451694</v>
       </c>
       <c r="N3">
-        <v>2.857415300000001</v>
+        <v>2.834830600000001</v>
       </c>
       <c r="O3">
-        <v>0.7143538250000002</v>
+        <v>0.7087076500000002</v>
       </c>
       <c r="P3">
-        <v>2.143061475000001</v>
+        <v>2.126122950000001</v>
       </c>
       <c r="Q3">
-        <v>4.113061475</v>
+        <v>4.096122950000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09370624057943618</v>
+        <v>0.09407378884228286</v>
       </c>
       <c r="T3">
-        <v>0.9602163969617189</v>
+        <v>0.9675834093674404</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>127.5199582017915</v>
+        <v>63.75997910089576</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0929468130654372</v>
+        <v>0.09274719795723256</v>
       </c>
       <c r="C4">
-        <v>41.82509141430894</v>
+        <v>41.52247485523739</v>
       </c>
       <c r="D4">
-        <v>42.16509141430894</v>
+        <v>42.31147485523739</v>
       </c>
       <c r="E4">
-        <v>-12.702</v>
+        <v>-12.253</v>
       </c>
       <c r="F4">
-        <v>0.898</v>
+        <v>1.347</v>
       </c>
       <c r="G4">
         <v>0.5580000000000001</v>
@@ -1603,28 +1603,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M4">
-        <v>0.0451694</v>
+        <v>0.0677541</v>
       </c>
       <c r="N4">
-        <v>2.834830600000001</v>
+        <v>2.812245900000001</v>
       </c>
       <c r="O4">
-        <v>0.7087076500000002</v>
+        <v>0.7030614750000002</v>
       </c>
       <c r="P4">
-        <v>2.126122950000001</v>
+        <v>2.109184425</v>
       </c>
       <c r="Q4">
-        <v>4.096122950000001</v>
+        <v>4.079184425</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09407378884228286</v>
+        <v>0.09444891541982739</v>
       </c>
       <c r="T4">
-        <v>0.9675834093674404</v>
+        <v>0.9751023189361661</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>63.75997910089576</v>
+        <v>42.5066527339305</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09274719795723256</v>
+        <v>0.09254758284902796</v>
       </c>
       <c r="C5">
-        <v>41.52247485523739</v>
+        <v>41.22087822813477</v>
       </c>
       <c r="D5">
-        <v>42.31147485523739</v>
+        <v>42.45887822813476</v>
       </c>
       <c r="E5">
-        <v>-12.253</v>
+        <v>-11.804</v>
       </c>
       <c r="F5">
-        <v>1.347</v>
+        <v>1.796</v>
       </c>
       <c r="G5">
         <v>0.5580000000000001</v>
@@ -1685,28 +1685,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M5">
-        <v>0.0677541</v>
+        <v>0.0903388</v>
       </c>
       <c r="N5">
-        <v>2.812245900000001</v>
+        <v>2.789661200000001</v>
       </c>
       <c r="O5">
-        <v>0.7030614750000002</v>
+        <v>0.6974153000000002</v>
       </c>
       <c r="P5">
-        <v>2.109184425</v>
+        <v>2.0922459</v>
       </c>
       <c r="Q5">
-        <v>4.079184425</v>
+        <v>4.062245900000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09444891541982739</v>
+        <v>0.09483185713440413</v>
       </c>
       <c r="T5">
-        <v>0.9751023189361661</v>
+        <v>0.9827778724542405</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.5066527339305</v>
+        <v>31.87998955044788</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09254758284902796</v>
+        <v>0.09234796774082335</v>
       </c>
       <c r="C6">
-        <v>41.22087822813477</v>
+        <v>40.92031222988642</v>
       </c>
       <c r="D6">
-        <v>42.45887822813476</v>
+        <v>42.60731222988642</v>
       </c>
       <c r="E6">
-        <v>-11.804</v>
+        <v>-11.355</v>
       </c>
       <c r="F6">
-        <v>1.796</v>
+        <v>2.245</v>
       </c>
       <c r="G6">
         <v>0.5580000000000001</v>
@@ -1767,28 +1767,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M6">
-        <v>0.0903388</v>
+        <v>0.1129235</v>
       </c>
       <c r="N6">
-        <v>2.789661200000001</v>
+        <v>2.767076500000001</v>
       </c>
       <c r="O6">
-        <v>0.6974153000000002</v>
+        <v>0.6917691250000002</v>
       </c>
       <c r="P6">
-        <v>2.0922459</v>
+        <v>2.075307375</v>
       </c>
       <c r="Q6">
-        <v>4.062245900000001</v>
+        <v>4.045307375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09483185713440413</v>
+        <v>0.09522286077981405</v>
       </c>
       <c r="T6">
-        <v>0.9827778724542405</v>
+        <v>0.9906150165726954</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.87998955044788</v>
+        <v>25.5039916403583</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09234796774082335</v>
+        <v>0.09214835263261874</v>
       </c>
       <c r="C7">
-        <v>40.92031222988642</v>
+        <v>40.62078770748541</v>
       </c>
       <c r="D7">
-        <v>42.60731222988642</v>
+        <v>42.75678770748541</v>
       </c>
       <c r="E7">
-        <v>-11.355</v>
+        <v>-10.906</v>
       </c>
       <c r="F7">
-        <v>2.245</v>
+        <v>2.694</v>
       </c>
       <c r="G7">
         <v>0.5580000000000001</v>
@@ -1849,28 +1849,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M7">
-        <v>0.1129235</v>
+        <v>0.1355082</v>
       </c>
       <c r="N7">
-        <v>2.767076500000001</v>
+        <v>2.744491800000001</v>
       </c>
       <c r="O7">
-        <v>0.6917691250000002</v>
+        <v>0.6861229500000002</v>
       </c>
       <c r="P7">
-        <v>2.075307375</v>
+        <v>2.058368850000001</v>
       </c>
       <c r="Q7">
-        <v>4.045307375</v>
+        <v>4.028368850000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09522286077981405</v>
+        <v>0.09562218365172206</v>
       </c>
       <c r="T7">
-        <v>0.9906150165726954</v>
+        <v>0.9986189084383514</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.5039916403583</v>
+        <v>21.25332636696525</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09214835263261874</v>
+        <v>0.09194873752441411</v>
       </c>
       <c r="C8">
-        <v>40.62078770748541</v>
+        <v>40.3223156606749</v>
       </c>
       <c r="D8">
-        <v>42.75678770748541</v>
+        <v>42.9073156606749</v>
       </c>
       <c r="E8">
-        <v>-10.906</v>
+        <v>-10.457</v>
       </c>
       <c r="F8">
-        <v>2.694</v>
+        <v>3.143</v>
       </c>
       <c r="G8">
         <v>0.5580000000000001</v>
@@ -1931,28 +1931,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M8">
-        <v>0.1355082</v>
+        <v>0.1580929</v>
       </c>
       <c r="N8">
-        <v>2.744491800000001</v>
+        <v>2.721907100000001</v>
       </c>
       <c r="O8">
-        <v>0.6861229500000002</v>
+        <v>0.6804767750000003</v>
       </c>
       <c r="P8">
-        <v>2.058368850000001</v>
+        <v>2.041430325000001</v>
       </c>
       <c r="Q8">
-        <v>4.028368850000001</v>
+        <v>4.011430325000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09562218365172206</v>
+        <v>0.09603009411227324</v>
       </c>
       <c r="T8">
-        <v>0.9986189084383514</v>
+        <v>1.006794927010796</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.25332636696525</v>
+        <v>18.21713688597022</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09194873752441411</v>
+        <v>0.09174912241620953</v>
       </c>
       <c r="C9">
-        <v>40.3223156606749</v>
+        <v>40.02490724464642</v>
       </c>
       <c r="D9">
-        <v>42.9073156606749</v>
+        <v>43.05890724464642</v>
       </c>
       <c r="E9">
-        <v>-10.457</v>
+        <v>-10.008</v>
       </c>
       <c r="F9">
-        <v>3.143</v>
+        <v>3.592</v>
       </c>
       <c r="G9">
         <v>0.5580000000000001</v>
@@ -2013,28 +2013,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M9">
-        <v>0.1580929</v>
+        <v>0.1806776</v>
       </c>
       <c r="N9">
-        <v>2.721907100000001</v>
+        <v>2.699322400000001</v>
       </c>
       <c r="O9">
-        <v>0.6804767750000001</v>
+        <v>0.6748306000000002</v>
       </c>
       <c r="P9">
-        <v>2.041430325</v>
+        <v>2.024491800000001</v>
       </c>
       <c r="Q9">
-        <v>4.011430325</v>
+        <v>3.9944918</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09603009411227324</v>
+        <v>0.09644687219153208</v>
       </c>
       <c r="T9">
-        <v>1.006794927010796</v>
+        <v>1.015148685117424</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.21713688597021</v>
+        <v>15.93999477522394</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09174912241620953</v>
+        <v>0.09154950730800489</v>
       </c>
       <c r="C10">
-        <v>40.02490724464642</v>
+        <v>39.72857377279573</v>
       </c>
       <c r="D10">
-        <v>43.05890724464642</v>
+        <v>43.21157377279573</v>
       </c>
       <c r="E10">
-        <v>-10.008</v>
+        <v>-9.559000000000001</v>
       </c>
       <c r="F10">
-        <v>3.592</v>
+        <v>4.040999999999999</v>
       </c>
       <c r="G10">
         <v>0.5580000000000001</v>
@@ -2095,28 +2095,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M10">
-        <v>0.1806776</v>
+        <v>0.2032623</v>
       </c>
       <c r="N10">
-        <v>2.699322400000001</v>
+        <v>2.676737700000001</v>
       </c>
       <c r="O10">
-        <v>0.6748306000000002</v>
+        <v>0.6691844250000002</v>
       </c>
       <c r="P10">
-        <v>2.024491800000001</v>
+        <v>2.007553275000001</v>
       </c>
       <c r="Q10">
-        <v>3.9944918</v>
+        <v>3.977553275000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09644687219153208</v>
+        <v>0.0968728102285768</v>
       </c>
       <c r="T10">
-        <v>1.015148685117424</v>
+        <v>1.023686042303318</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.93999477522394</v>
+        <v>14.1688842446435</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09154950730800489</v>
+        <v>0.09146239219980028</v>
       </c>
       <c r="C11">
-        <v>39.72857377279573</v>
+        <v>39.34653963963227</v>
       </c>
       <c r="D11">
-        <v>43.21157377279573</v>
+        <v>43.27853963963227</v>
       </c>
       <c r="E11">
-        <v>-9.559000000000001</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="F11">
-        <v>4.040999999999999</v>
+        <v>4.489999999999999</v>
       </c>
       <c r="G11">
         <v>0.5580000000000001</v>
@@ -2177,45 +2177,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M11">
-        <v>0.2032623</v>
+        <v>0.232582</v>
       </c>
       <c r="N11">
-        <v>2.676737700000001</v>
+        <v>2.647418000000001</v>
       </c>
       <c r="O11">
-        <v>0.6691844250000002</v>
+        <v>0.6618545000000002</v>
       </c>
       <c r="P11">
-        <v>2.007553275000001</v>
+        <v>1.985563500000001</v>
       </c>
       <c r="Q11">
-        <v>3.977553275000001</v>
+        <v>3.955563500000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0968728102285768</v>
+        <v>0.09730821355533364</v>
       </c>
       <c r="T11">
-        <v>1.023686042303318</v>
+        <v>1.032413118537788</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>14.1688842446435</v>
+        <v>12.38272953195003</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09146239219980028</v>
+        <v>0.09127402709159567</v>
       </c>
       <c r="C12">
-        <v>39.34653963963227</v>
+        <v>39.04304892424263</v>
       </c>
       <c r="D12">
-        <v>43.27853963963227</v>
+        <v>43.42404892424263</v>
       </c>
       <c r="E12">
-        <v>-9.109999999999999</v>
+        <v>-8.661</v>
       </c>
       <c r="F12">
-        <v>4.49</v>
+        <v>4.939</v>
       </c>
       <c r="G12">
         <v>0.5580000000000001</v>
@@ -2259,28 +2259,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M12">
-        <v>0.232582</v>
+        <v>0.2558402</v>
       </c>
       <c r="N12">
-        <v>2.647418000000001</v>
+        <v>2.624159800000001</v>
       </c>
       <c r="O12">
-        <v>0.6618545000000002</v>
+        <v>0.6560399500000001</v>
       </c>
       <c r="P12">
-        <v>1.985563500000001</v>
+        <v>1.96811985</v>
       </c>
       <c r="Q12">
-        <v>3.955563500000001</v>
+        <v>3.938119850000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09730821355533364</v>
+        <v>0.09775340122651198</v>
       </c>
       <c r="T12">
-        <v>1.032413118537788</v>
+        <v>1.041336308844943</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.38272953195002</v>
+        <v>11.25702684722729</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09127402709159567</v>
+        <v>0.09108566198339105</v>
       </c>
       <c r="C13">
-        <v>39.04304892424263</v>
+        <v>38.74053996004152</v>
       </c>
       <c r="D13">
-        <v>43.42404892424263</v>
+        <v>43.57053996004151</v>
       </c>
       <c r="E13">
-        <v>-8.661</v>
+        <v>-8.212</v>
       </c>
       <c r="F13">
-        <v>4.939</v>
+        <v>5.388</v>
       </c>
       <c r="G13">
         <v>0.5580000000000001</v>
@@ -2341,28 +2341,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M13">
-        <v>0.2558402</v>
+        <v>0.2790984</v>
       </c>
       <c r="N13">
-        <v>2.624159800000001</v>
+        <v>2.600901600000001</v>
       </c>
       <c r="O13">
-        <v>0.6560399500000001</v>
+        <v>0.6502254000000002</v>
       </c>
       <c r="P13">
-        <v>1.96811985</v>
+        <v>1.950676200000001</v>
       </c>
       <c r="Q13">
-        <v>3.938119850000001</v>
+        <v>3.920676200000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09775340122651198</v>
+        <v>0.098208706799308</v>
       </c>
       <c r="T13">
-        <v>1.041336308844943</v>
+        <v>1.050462298931805</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.25702684722729</v>
+        <v>10.31894127662502</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09108566198339105</v>
+        <v>0.09106304687518642</v>
       </c>
       <c r="C14">
-        <v>38.74053996004152</v>
+        <v>38.30919415107829</v>
       </c>
       <c r="D14">
-        <v>43.57053996004151</v>
+        <v>43.58819415107829</v>
       </c>
       <c r="E14">
-        <v>-8.212</v>
+        <v>-7.763</v>
       </c>
       <c r="F14">
-        <v>5.388</v>
+        <v>5.837</v>
       </c>
       <c r="G14">
         <v>0.5580000000000001</v>
@@ -2423,45 +2423,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M14">
-        <v>0.2790984</v>
+        <v>0.3122795</v>
       </c>
       <c r="N14">
-        <v>2.600901600000001</v>
+        <v>2.567720500000001</v>
       </c>
       <c r="O14">
-        <v>0.6502254000000002</v>
+        <v>0.6419301250000002</v>
       </c>
       <c r="P14">
-        <v>1.950676200000001</v>
+        <v>1.925790375000001</v>
       </c>
       <c r="Q14">
-        <v>3.920676200000001</v>
+        <v>3.895790375000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.098208706799308</v>
+        <v>0.09867447916688094</v>
       </c>
       <c r="T14">
-        <v>1.050462298931805</v>
+        <v>1.059798081894228</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.31894127662502</v>
+        <v>9.222507401222305</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09106304687518642</v>
+        <v>0.0908874317669818</v>
       </c>
       <c r="C15">
-        <v>38.30919415107829</v>
+        <v>37.99777424243253</v>
       </c>
       <c r="D15">
-        <v>43.58819415107829</v>
+        <v>43.72577424243253</v>
       </c>
       <c r="E15">
-        <v>-7.763</v>
+        <v>-7.313999999999999</v>
       </c>
       <c r="F15">
-        <v>5.837</v>
+        <v>6.286</v>
       </c>
       <c r="G15">
         <v>0.5580000000000001</v>
@@ -2505,28 +2505,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M15">
-        <v>0.3122795</v>
+        <v>0.336301</v>
       </c>
       <c r="N15">
-        <v>2.567720500000001</v>
+        <v>2.543699000000001</v>
       </c>
       <c r="O15">
-        <v>0.6419301250000002</v>
+        <v>0.6359247500000001</v>
       </c>
       <c r="P15">
-        <v>1.925790375000001</v>
+        <v>1.907774250000001</v>
       </c>
       <c r="Q15">
-        <v>3.895790375000001</v>
+        <v>3.877774250000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09867447916688094</v>
+        <v>0.09915108344997885</v>
       </c>
       <c r="T15">
-        <v>1.059798081894228</v>
+        <v>1.069350976088335</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.222507401222305</v>
+        <v>8.563756872563568</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0908874317669818</v>
+        <v>0.09071181665877719</v>
       </c>
       <c r="C16">
-        <v>37.99777424243253</v>
+        <v>37.68722558874813</v>
       </c>
       <c r="D16">
-        <v>43.72577424243253</v>
+        <v>43.86422558874813</v>
       </c>
       <c r="E16">
-        <v>-7.313999999999999</v>
+        <v>-6.864999999999998</v>
       </c>
       <c r="F16">
-        <v>6.286</v>
+        <v>6.735000000000001</v>
       </c>
       <c r="G16">
         <v>0.5580000000000001</v>
@@ -2587,28 +2587,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M16">
-        <v>0.336301</v>
+        <v>0.3603225</v>
       </c>
       <c r="N16">
-        <v>2.543699000000001</v>
+        <v>2.519677500000001</v>
       </c>
       <c r="O16">
-        <v>0.6359247500000001</v>
+        <v>0.6299193750000002</v>
       </c>
       <c r="P16">
-        <v>1.907774250000001</v>
+        <v>1.889758125000001</v>
       </c>
       <c r="Q16">
-        <v>3.877774250000001</v>
+        <v>3.859758125000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09915108344997885</v>
+        <v>0.09963890195150257</v>
       </c>
       <c r="T16">
-        <v>1.069350976088335</v>
+        <v>1.07912864426348</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.563756872563568</v>
+        <v>7.992839747725997</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09071181665877719</v>
+        <v>0.09063220155057256</v>
       </c>
       <c r="C17">
-        <v>37.68722558874813</v>
+        <v>37.30128176318019</v>
       </c>
       <c r="D17">
-        <v>43.86422558874813</v>
+        <v>43.92728176318018</v>
       </c>
       <c r="E17">
-        <v>-6.865</v>
+        <v>-6.415999999999999</v>
       </c>
       <c r="F17">
-        <v>6.734999999999999</v>
+        <v>7.184</v>
       </c>
       <c r="G17">
         <v>0.5580000000000001</v>
@@ -2669,45 +2669,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M17">
-        <v>0.3603225</v>
+        <v>0.3900912</v>
       </c>
       <c r="N17">
-        <v>2.519677500000001</v>
+        <v>2.489908800000001</v>
       </c>
       <c r="O17">
-        <v>0.6299193750000002</v>
+        <v>0.6224772000000002</v>
       </c>
       <c r="P17">
-        <v>1.889758125000001</v>
+        <v>1.867431600000001</v>
       </c>
       <c r="Q17">
-        <v>3.859758125000001</v>
+        <v>3.8374316</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09963890195150257</v>
+        <v>0.1001383351792531</v>
       </c>
       <c r="T17">
-        <v>1.07912864426348</v>
+        <v>1.089139114061842</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.992839747725998</v>
+        <v>7.382888924436133</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09063220155057256</v>
+        <v>0.09046258644236796</v>
       </c>
       <c r="C18">
-        <v>37.30128176318019</v>
+        <v>36.98722546665115</v>
       </c>
       <c r="D18">
-        <v>43.92728176318018</v>
+        <v>44.06222546665116</v>
       </c>
       <c r="E18">
-        <v>-6.415999999999999</v>
+        <v>-5.967</v>
       </c>
       <c r="F18">
-        <v>7.184</v>
+        <v>7.633</v>
       </c>
       <c r="G18">
         <v>0.5580000000000001</v>
@@ -2751,28 +2751,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M18">
-        <v>0.3900912</v>
+        <v>0.4144719</v>
       </c>
       <c r="N18">
-        <v>2.489908800000001</v>
+        <v>2.465528100000001</v>
       </c>
       <c r="O18">
-        <v>0.6224772000000002</v>
+        <v>0.6163820250000002</v>
       </c>
       <c r="P18">
-        <v>1.867431600000001</v>
+        <v>1.849146075000001</v>
       </c>
       <c r="Q18">
-        <v>3.8374316</v>
+        <v>3.819146075000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1001383351792531</v>
+        <v>0.100649802942612</v>
       </c>
       <c r="T18">
-        <v>1.089139114061842</v>
+        <v>1.099390799999925</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.382888924436133</v>
+        <v>6.948601340645773</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09046258644236796</v>
+        <v>0.09029297133416334</v>
       </c>
       <c r="C19">
-        <v>36.98722546665115</v>
+        <v>36.6740008134604</v>
       </c>
       <c r="D19">
-        <v>44.06222546665116</v>
+        <v>44.1980008134604</v>
       </c>
       <c r="E19">
-        <v>-5.967</v>
+        <v>-5.517999999999999</v>
       </c>
       <c r="F19">
-        <v>7.633</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="G19">
         <v>0.5580000000000001</v>
@@ -2833,28 +2833,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M19">
-        <v>0.4144719</v>
+        <v>0.4388526</v>
       </c>
       <c r="N19">
-        <v>2.465528100000001</v>
+        <v>2.441147400000001</v>
       </c>
       <c r="O19">
-        <v>0.6163820250000002</v>
+        <v>0.6102868500000002</v>
       </c>
       <c r="P19">
-        <v>1.849146075000001</v>
+        <v>1.830860550000001</v>
       </c>
       <c r="Q19">
-        <v>3.819146075000001</v>
+        <v>3.80086055</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.100649802942612</v>
+        <v>0.1011737455294675</v>
       </c>
       <c r="T19">
-        <v>1.099390799999925</v>
+        <v>1.109892527058447</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.948601340645773</v>
+        <v>6.562567932832118</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09029297133416335</v>
+        <v>0.09012335622595874</v>
       </c>
       <c r="C20">
-        <v>36.67400081346038</v>
+        <v>36.36161551536208</v>
       </c>
       <c r="D20">
-        <v>44.19800081346038</v>
+        <v>44.33461551536208</v>
       </c>
       <c r="E20">
-        <v>-5.518000000000001</v>
+        <v>-5.068999999999999</v>
       </c>
       <c r="F20">
-        <v>8.081999999999999</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="G20">
         <v>0.5580000000000001</v>
@@ -2915,28 +2915,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M20">
-        <v>0.4388525999999999</v>
+        <v>0.4632333</v>
       </c>
       <c r="N20">
-        <v>2.441147400000001</v>
+        <v>2.416766700000001</v>
       </c>
       <c r="O20">
-        <v>0.6102868500000003</v>
+        <v>0.6041916750000002</v>
       </c>
       <c r="P20">
-        <v>1.830860550000001</v>
+        <v>1.812575025000001</v>
       </c>
       <c r="Q20">
-        <v>3.800860550000001</v>
+        <v>3.782575025000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1011737455294675</v>
+        <v>0.1017106249703194</v>
       </c>
       <c r="T20">
-        <v>1.109892527058447</v>
+        <v>1.12065355601965</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.56256793283212</v>
+        <v>6.217169620577796</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09012335622595874</v>
+        <v>0.09010374111775411</v>
       </c>
       <c r="C21">
-        <v>36.36161551536208</v>
+        <v>35.92846879800267</v>
       </c>
       <c r="D21">
-        <v>44.33461551536208</v>
+        <v>44.35046879800267</v>
       </c>
       <c r="E21">
-        <v>-5.068999999999999</v>
+        <v>-4.619999999999999</v>
       </c>
       <c r="F21">
-        <v>8.531000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G21">
         <v>0.5580000000000001</v>
@@ -2997,45 +2997,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M21">
-        <v>0.4632333</v>
+        <v>0.496594</v>
       </c>
       <c r="N21">
-        <v>2.416766700000001</v>
+        <v>2.383406000000001</v>
       </c>
       <c r="O21">
-        <v>0.6041916750000002</v>
+        <v>0.5958515000000002</v>
       </c>
       <c r="P21">
-        <v>1.812575025000001</v>
+        <v>1.787554500000001</v>
       </c>
       <c r="Q21">
-        <v>3.782575025000001</v>
+        <v>3.7575545</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1017106249703194</v>
+        <v>0.1022609263971926</v>
       </c>
       <c r="T21">
-        <v>1.12065355601965</v>
+        <v>1.131683610704883</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.217169620577796</v>
+        <v>5.799506236482923</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09010374111775411</v>
+        <v>0.0899416260095495</v>
       </c>
       <c r="C22">
-        <v>35.92846879800267</v>
+        <v>35.61092850078185</v>
       </c>
       <c r="D22">
-        <v>44.35046879800267</v>
+        <v>44.48192850078185</v>
       </c>
       <c r="E22">
-        <v>-4.619999999999999</v>
+        <v>-4.170999999999999</v>
       </c>
       <c r="F22">
-        <v>8.98</v>
+        <v>9.429</v>
       </c>
       <c r="G22">
         <v>0.5580000000000001</v>
@@ -3079,28 +3079,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M22">
-        <v>0.496594</v>
+        <v>0.5214237</v>
       </c>
       <c r="N22">
-        <v>2.383406000000001</v>
+        <v>2.358576300000001</v>
       </c>
       <c r="O22">
-        <v>0.5958515000000002</v>
+        <v>0.5896440750000002</v>
       </c>
       <c r="P22">
-        <v>1.787554500000001</v>
+        <v>1.768932225</v>
       </c>
       <c r="Q22">
-        <v>3.7575545</v>
+        <v>3.738932225</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1022609263971926</v>
+        <v>0.1028251595057589</v>
       </c>
       <c r="T22">
-        <v>1.131683610704883</v>
+        <v>1.142992907280881</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.799506236482923</v>
+        <v>5.523339272840879</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0899416260095495</v>
+        <v>0.08977951090134488</v>
       </c>
       <c r="C23">
-        <v>35.61092850078185</v>
+        <v>35.29416984267091</v>
       </c>
       <c r="D23">
-        <v>44.48192850078185</v>
+        <v>44.61416984267091</v>
       </c>
       <c r="E23">
-        <v>-4.171000000000001</v>
+        <v>-3.722</v>
       </c>
       <c r="F23">
-        <v>9.428999999999998</v>
+        <v>9.878</v>
       </c>
       <c r="G23">
         <v>0.5580000000000001</v>
@@ -3161,28 +3161,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M23">
-        <v>0.5214236999999999</v>
+        <v>0.5462534</v>
       </c>
       <c r="N23">
-        <v>2.358576300000001</v>
+        <v>2.333746600000001</v>
       </c>
       <c r="O23">
-        <v>0.5896440750000003</v>
+        <v>0.5834366500000002</v>
       </c>
       <c r="P23">
-        <v>1.768932225000001</v>
+        <v>1.750309950000001</v>
       </c>
       <c r="Q23">
-        <v>3.738932225000001</v>
+        <v>3.720309950000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1028251595057589</v>
+        <v>0.1034038601299293</v>
       </c>
       <c r="T23">
-        <v>1.142992907280881</v>
+        <v>1.154592185820366</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.523339272840881</v>
+        <v>5.272278396802657</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08977951090134488</v>
+        <v>0.08961739579314026</v>
       </c>
       <c r="C24">
-        <v>35.29416984267091</v>
+        <v>34.97819981571501</v>
       </c>
       <c r="D24">
-        <v>44.61416984267091</v>
+        <v>44.74719981571501</v>
       </c>
       <c r="E24">
-        <v>-3.722</v>
+        <v>-3.273</v>
       </c>
       <c r="F24">
-        <v>9.878</v>
+        <v>10.327</v>
       </c>
       <c r="G24">
         <v>0.5580000000000001</v>
@@ -3243,28 +3243,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M24">
-        <v>0.5462534</v>
+        <v>0.5710831000000001</v>
       </c>
       <c r="N24">
-        <v>2.333746600000001</v>
+        <v>2.308916900000001</v>
       </c>
       <c r="O24">
-        <v>0.5834366500000002</v>
+        <v>0.5772292250000002</v>
       </c>
       <c r="P24">
-        <v>1.750309950000001</v>
+        <v>1.731687675000001</v>
       </c>
       <c r="Q24">
-        <v>3.720309950000001</v>
+        <v>3.701687675000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1034038601299293</v>
+        <v>0.1039975919391432</v>
       </c>
       <c r="T24">
-        <v>1.154592185820366</v>
+        <v>1.166492744321916</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.272278396802657</v>
+        <v>5.043048901289498</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08961739579314026</v>
+        <v>0.08945528068493565</v>
       </c>
       <c r="C25">
-        <v>34.97819981571501</v>
+        <v>34.66302549560385</v>
       </c>
       <c r="D25">
-        <v>44.74719981571501</v>
+        <v>44.88102549560385</v>
       </c>
       <c r="E25">
-        <v>-3.273</v>
+        <v>-2.824</v>
       </c>
       <c r="F25">
-        <v>10.327</v>
+        <v>10.776</v>
       </c>
       <c r="G25">
         <v>0.5580000000000001</v>
@@ -3325,28 +3325,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M25">
-        <v>0.5710831000000001</v>
+        <v>0.5959128</v>
       </c>
       <c r="N25">
-        <v>2.308916900000001</v>
+        <v>2.284087200000001</v>
       </c>
       <c r="O25">
-        <v>0.5772292250000002</v>
+        <v>0.5710218000000002</v>
       </c>
       <c r="P25">
-        <v>1.731687675000001</v>
+        <v>1.713065400000001</v>
       </c>
       <c r="Q25">
-        <v>3.701687675000001</v>
+        <v>3.683065400000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1039975919391432</v>
+        <v>0.1046069482696522</v>
       </c>
       <c r="T25">
-        <v>1.166492744321916</v>
+        <v>1.178706475415612</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.043048901289498</v>
+        <v>4.83292186373577</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08945528068493565</v>
+        <v>0.08929316557673103</v>
       </c>
       <c r="C26">
-        <v>34.66302549560385</v>
+        <v>34.34865404292626</v>
       </c>
       <c r="D26">
-        <v>44.88102549560385</v>
+        <v>45.01565404292626</v>
       </c>
       <c r="E26">
-        <v>-2.824</v>
+        <v>-2.375</v>
       </c>
       <c r="F26">
-        <v>10.776</v>
+        <v>11.225</v>
       </c>
       <c r="G26">
         <v>0.5580000000000001</v>
@@ -3407,28 +3407,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M26">
-        <v>0.5959128</v>
+        <v>0.6207425</v>
       </c>
       <c r="N26">
-        <v>2.284087200000001</v>
+        <v>2.259257500000001</v>
       </c>
       <c r="O26">
-        <v>0.5710218000000002</v>
+        <v>0.5648143750000002</v>
       </c>
       <c r="P26">
-        <v>1.713065400000001</v>
+        <v>1.694443125000001</v>
       </c>
       <c r="Q26">
-        <v>3.683065400000001</v>
+        <v>3.664443125000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1046069482696522</v>
+        <v>0.105232554102308</v>
       </c>
       <c r="T26">
-        <v>1.178706475415612</v>
+        <v>1.19124590600514</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.83292186373577</v>
+        <v>4.639604989186338</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08929316557673103</v>
+        <v>0.08961855046852642</v>
       </c>
       <c r="C27">
-        <v>34.34865404292626</v>
+        <v>33.63024949598849</v>
       </c>
       <c r="D27">
-        <v>45.01565404292626</v>
+        <v>44.74624949598849</v>
       </c>
       <c r="E27">
-        <v>-2.375</v>
+        <v>-1.926</v>
       </c>
       <c r="F27">
-        <v>11.225</v>
+        <v>11.674</v>
       </c>
       <c r="G27">
         <v>0.5580000000000001</v>
@@ -3489,45 +3489,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M27">
-        <v>0.6207425</v>
+        <v>0.6747572000000001</v>
       </c>
       <c r="N27">
-        <v>2.259257500000001</v>
+        <v>2.205242800000001</v>
       </c>
       <c r="O27">
-        <v>0.5648143750000002</v>
+        <v>0.5513107000000002</v>
       </c>
       <c r="P27">
-        <v>1.694443125000001</v>
+        <v>1.6539321</v>
       </c>
       <c r="Q27">
-        <v>3.664443125000001</v>
+        <v>3.6239321</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.105232554102308</v>
+        <v>0.1058750682007114</v>
       </c>
       <c r="T27">
-        <v>1.19124590600514</v>
+        <v>1.204124240124115</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.639604989186338</v>
+        <v>4.268201954717934</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08961855046852642</v>
+        <v>0.0894751853603218</v>
       </c>
       <c r="C28">
-        <v>33.63024949598849</v>
+        <v>33.2995511363995</v>
       </c>
       <c r="D28">
-        <v>44.74624949598849</v>
+        <v>44.8645511363995</v>
       </c>
       <c r="E28">
-        <v>-1.926</v>
+        <v>-1.476999999999999</v>
       </c>
       <c r="F28">
-        <v>11.674</v>
+        <v>12.123</v>
       </c>
       <c r="G28">
         <v>0.5580000000000001</v>
@@ -3571,28 +3571,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M28">
-        <v>0.6747572000000001</v>
+        <v>0.7007094000000001</v>
       </c>
       <c r="N28">
-        <v>2.205242800000001</v>
+        <v>2.179290600000001</v>
       </c>
       <c r="O28">
-        <v>0.5513107000000002</v>
+        <v>0.5448226500000002</v>
       </c>
       <c r="P28">
-        <v>1.6539321</v>
+        <v>1.634467950000001</v>
       </c>
       <c r="Q28">
-        <v>3.6239321</v>
+        <v>3.604467950000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1058750682007114</v>
+        <v>0.1065351854250983</v>
       </c>
       <c r="T28">
-        <v>1.204124240124115</v>
+        <v>1.217355405314842</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.268201954717934</v>
+        <v>4.110120400839492</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0894751853603218</v>
+        <v>0.09006682025211718</v>
       </c>
       <c r="C29">
-        <v>33.2995511363995</v>
+        <v>32.36633967988944</v>
       </c>
       <c r="D29">
-        <v>44.8645511363995</v>
+        <v>44.38033967988944</v>
       </c>
       <c r="E29">
-        <v>-1.476999999999999</v>
+        <v>-1.027999999999999</v>
       </c>
       <c r="F29">
-        <v>12.123</v>
+        <v>12.572</v>
       </c>
       <c r="G29">
         <v>0.5580000000000001</v>
@@ -3653,45 +3653,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M29">
-        <v>0.7007094000000001</v>
+        <v>0.7706636000000001</v>
       </c>
       <c r="N29">
-        <v>2.179290600000001</v>
+        <v>2.109336400000001</v>
       </c>
       <c r="O29">
-        <v>0.5448226500000002</v>
+        <v>0.5273341000000001</v>
       </c>
       <c r="P29">
-        <v>1.634467950000001</v>
+        <v>1.582002300000001</v>
       </c>
       <c r="Q29">
-        <v>3.604467950000001</v>
+        <v>3.552002300000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1065351854250983</v>
+        <v>0.1072136392390516</v>
       </c>
       <c r="T29">
-        <v>1.217355405314842</v>
+        <v>1.230954102871978</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.110120400839492</v>
+        <v>3.737039092024069</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09006682025211718</v>
+        <v>0.08994970514391257</v>
       </c>
       <c r="C30">
-        <v>32.36633967988944</v>
+        <v>32.01235865416253</v>
       </c>
       <c r="D30">
-        <v>44.38033967988944</v>
+        <v>44.47535865416253</v>
       </c>
       <c r="E30">
-        <v>-1.027999999999999</v>
+        <v>-0.5789999999999988</v>
       </c>
       <c r="F30">
-        <v>12.572</v>
+        <v>13.021</v>
       </c>
       <c r="G30">
         <v>0.5580000000000001</v>
@@ -3735,28 +3735,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M30">
-        <v>0.7706636000000001</v>
+        <v>0.7981873</v>
       </c>
       <c r="N30">
-        <v>2.109336400000001</v>
+        <v>2.081812700000001</v>
       </c>
       <c r="O30">
-        <v>0.5273341000000001</v>
+        <v>0.5204531750000002</v>
       </c>
       <c r="P30">
-        <v>1.582002300000001</v>
+        <v>1.561359525000001</v>
       </c>
       <c r="Q30">
-        <v>3.552002300000001</v>
+        <v>3.531359525000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1072136392390516</v>
+        <v>0.1079112044280459</v>
       </c>
       <c r="T30">
-        <v>1.230954102871978</v>
+        <v>1.244935862332132</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.737039092024069</v>
+        <v>3.608175675057722</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08994970514391257</v>
+        <v>0.09046259003570795</v>
       </c>
       <c r="C31">
-        <v>32.01235865416253</v>
+        <v>31.15022259905182</v>
       </c>
       <c r="D31">
-        <v>44.47535865416253</v>
+        <v>44.06222259905182</v>
       </c>
       <c r="E31">
-        <v>-0.5790000000000006</v>
+        <v>-0.1300000000000008</v>
       </c>
       <c r="F31">
-        <v>13.021</v>
+        <v>13.47</v>
       </c>
       <c r="G31">
         <v>0.5580000000000001</v>
@@ -3817,45 +3817,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M31">
-        <v>0.7981872999999999</v>
+        <v>0.8634269999999999</v>
       </c>
       <c r="N31">
-        <v>2.081812700000001</v>
+        <v>2.016573000000001</v>
       </c>
       <c r="O31">
-        <v>0.5204531750000002</v>
+        <v>0.5041432500000003</v>
       </c>
       <c r="P31">
-        <v>1.561359525000001</v>
+        <v>1.512429750000001</v>
       </c>
       <c r="Q31">
-        <v>3.531359525000001</v>
+        <v>3.482429750000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1079112044280459</v>
+        <v>0.1086287000510114</v>
       </c>
       <c r="T31">
-        <v>1.244935862332132</v>
+        <v>1.259317100634005</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.608175675057723</v>
+        <v>3.335545448544001</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09046259003570795</v>
+        <v>0.09036647492750333</v>
       </c>
       <c r="C32">
-        <v>31.15022259905182</v>
+        <v>30.77805925671679</v>
       </c>
       <c r="D32">
-        <v>44.06222259905182</v>
+        <v>44.13905925671678</v>
       </c>
       <c r="E32">
-        <v>-0.1300000000000008</v>
+        <v>0.3189999999999991</v>
       </c>
       <c r="F32">
-        <v>13.47</v>
+        <v>13.919</v>
       </c>
       <c r="G32">
         <v>0.5580000000000001</v>
@@ -3899,28 +3899,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M32">
-        <v>0.8634269999999999</v>
+        <v>0.8922078999999999</v>
       </c>
       <c r="N32">
-        <v>2.016573000000001</v>
+        <v>1.987792100000001</v>
       </c>
       <c r="O32">
-        <v>0.5041432500000003</v>
+        <v>0.4969480250000002</v>
       </c>
       <c r="P32">
-        <v>1.512429750000001</v>
+        <v>1.490844075000001</v>
       </c>
       <c r="Q32">
-        <v>3.482429750000001</v>
+        <v>3.460844075000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1086287000510114</v>
+        <v>0.1093669926485555</v>
       </c>
       <c r="T32">
-        <v>1.259317100634005</v>
+        <v>1.274115186422889</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.335545448544001</v>
+        <v>3.227947208268388</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09036647492750333</v>
+        <v>0.09027035981929871</v>
       </c>
       <c r="C33">
-        <v>30.77805925671679</v>
+        <v>30.40616436135953</v>
       </c>
       <c r="D33">
-        <v>44.13905925671678</v>
+        <v>44.21616436135953</v>
       </c>
       <c r="E33">
-        <v>0.3189999999999991</v>
+        <v>0.7680000000000007</v>
       </c>
       <c r="F33">
-        <v>13.919</v>
+        <v>14.368</v>
       </c>
       <c r="G33">
         <v>0.5580000000000001</v>
@@ -3981,28 +3981,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M33">
-        <v>0.8922078999999999</v>
+        <v>0.9209888000000001</v>
       </c>
       <c r="N33">
-        <v>1.987792100000001</v>
+        <v>1.959011200000001</v>
       </c>
       <c r="O33">
-        <v>0.4969480250000002</v>
+        <v>0.4897528000000002</v>
       </c>
       <c r="P33">
-        <v>1.490844075000001</v>
+        <v>1.469258400000001</v>
       </c>
       <c r="Q33">
-        <v>3.460844075000001</v>
+        <v>3.439258400000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1093669926485555</v>
+        <v>0.1101269997342628</v>
       </c>
       <c r="T33">
-        <v>1.274115186422889</v>
+        <v>1.289348510029093</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.227947208268388</v>
+        <v>3.127073858010001</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09027035981929871</v>
+        <v>0.09017424471109409</v>
       </c>
       <c r="C34">
-        <v>30.40616436135953</v>
+        <v>30.03453932226608</v>
       </c>
       <c r="D34">
-        <v>44.21616436135953</v>
+        <v>44.29353932226608</v>
       </c>
       <c r="E34">
-        <v>0.7680000000000007</v>
+        <v>1.217000000000001</v>
       </c>
       <c r="F34">
-        <v>14.368</v>
+        <v>14.817</v>
       </c>
       <c r="G34">
         <v>0.5580000000000001</v>
@@ -4063,28 +4063,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M34">
-        <v>0.9209888000000001</v>
+        <v>0.9497697000000001</v>
       </c>
       <c r="N34">
-        <v>1.959011200000001</v>
+        <v>1.930230300000001</v>
       </c>
       <c r="O34">
-        <v>0.4897528000000002</v>
+        <v>0.4825575750000002</v>
       </c>
       <c r="P34">
-        <v>1.469258400000001</v>
+        <v>1.447672725000001</v>
       </c>
       <c r="Q34">
-        <v>3.439258400000001</v>
+        <v>3.417672725000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1101269997342628</v>
+        <v>0.1109096935986479</v>
       </c>
       <c r="T34">
-        <v>1.289348510029093</v>
+        <v>1.305036559713094</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.127073858010001</v>
+        <v>3.03231404413091</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09017424471109409</v>
+        <v>0.09206712960288949</v>
       </c>
       <c r="C35">
-        <v>30.03453932226608</v>
+        <v>28.10990963605591</v>
       </c>
       <c r="D35">
-        <v>44.29353932226608</v>
+        <v>42.81790963605591</v>
       </c>
       <c r="E35">
-        <v>1.217000000000001</v>
+        <v>1.666</v>
       </c>
       <c r="F35">
-        <v>14.817</v>
+        <v>15.266</v>
       </c>
       <c r="G35">
         <v>0.5580000000000001</v>
@@ -4145,45 +4145,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M35">
-        <v>0.9497697000000001</v>
+        <v>1.0976254</v>
       </c>
       <c r="N35">
-        <v>1.930230300000001</v>
+        <v>1.782374600000001</v>
       </c>
       <c r="O35">
-        <v>0.4825575750000002</v>
+        <v>0.4455936500000002</v>
       </c>
       <c r="P35">
-        <v>1.447672725000001</v>
+        <v>1.336780950000001</v>
       </c>
       <c r="Q35">
-        <v>3.417672725000001</v>
+        <v>3.30678095</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1109096935986479</v>
+        <v>0.1117161054589235</v>
       </c>
       <c r="T35">
-        <v>1.305036559713094</v>
+        <v>1.321200004842064</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.03231404413091</v>
+        <v>2.623845986071387</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09206712960288949</v>
+        <v>0.09202951449468486</v>
       </c>
       <c r="C36">
-        <v>28.10990963605591</v>
+        <v>27.68927498826699</v>
       </c>
       <c r="D36">
-        <v>42.81790963605591</v>
+        <v>42.84627498826699</v>
       </c>
       <c r="E36">
-        <v>1.666</v>
+        <v>2.115000000000002</v>
       </c>
       <c r="F36">
-        <v>15.266</v>
+        <v>15.715</v>
       </c>
       <c r="G36">
         <v>0.5580000000000001</v>
@@ -4227,28 +4227,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M36">
-        <v>1.0976254</v>
+        <v>1.1299085</v>
       </c>
       <c r="N36">
-        <v>1.782374600000001</v>
+        <v>1.750091500000001</v>
       </c>
       <c r="O36">
-        <v>0.4455936500000002</v>
+        <v>0.4375228750000001</v>
       </c>
       <c r="P36">
-        <v>1.336780950000001</v>
+        <v>1.312568625</v>
       </c>
       <c r="Q36">
-        <v>3.30678095</v>
+        <v>3.282568625000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1117161054589235</v>
+        <v>0.1125473299918229</v>
       </c>
       <c r="T36">
-        <v>1.321200004842064</v>
+        <v>1.337860786744234</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.623845986071387</v>
+        <v>2.548878957897919</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09202951449468486</v>
+        <v>0.09304489938648025</v>
       </c>
       <c r="C37">
-        <v>27.68927498826699</v>
+        <v>26.4875324250912</v>
       </c>
       <c r="D37">
-        <v>42.84627498826699</v>
+        <v>42.0935324250912</v>
       </c>
       <c r="E37">
-        <v>2.115000000000002</v>
+        <v>2.564000000000002</v>
       </c>
       <c r="F37">
-        <v>15.715</v>
+        <v>16.164</v>
       </c>
       <c r="G37">
         <v>0.5580000000000001</v>
@@ -4309,45 +4309,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M37">
-        <v>1.1299085</v>
+        <v>1.2252312</v>
       </c>
       <c r="N37">
-        <v>1.750091500000001</v>
+        <v>1.6547688</v>
       </c>
       <c r="O37">
-        <v>0.4375228750000001</v>
+        <v>0.4136922000000001</v>
       </c>
       <c r="P37">
-        <v>1.312568625</v>
+        <v>1.2410766</v>
       </c>
       <c r="Q37">
-        <v>3.282568625000001</v>
+        <v>3.2110766</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1125473299918229</v>
+        <v>0.1134045302913754</v>
       </c>
       <c r="T37">
-        <v>1.337860786744234</v>
+        <v>1.355042218080847</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.548878957897919</v>
+        <v>2.35057677277562</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09304489938648025</v>
+        <v>0.09303653427827564</v>
       </c>
       <c r="C38">
-        <v>26.4875324250912</v>
+        <v>26.04462572428664</v>
       </c>
       <c r="D38">
-        <v>42.0935324250912</v>
+        <v>42.09962572428664</v>
       </c>
       <c r="E38">
-        <v>2.563999999999998</v>
+        <v>3.013</v>
       </c>
       <c r="F38">
-        <v>16.164</v>
+        <v>16.613</v>
       </c>
       <c r="G38">
         <v>0.5580000000000001</v>
@@ -4391,28 +4391,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M38">
-        <v>1.2252312</v>
+        <v>1.2592654</v>
       </c>
       <c r="N38">
-        <v>1.654768800000001</v>
+        <v>1.620734600000001</v>
       </c>
       <c r="O38">
-        <v>0.4136922000000002</v>
+        <v>0.4051836500000002</v>
       </c>
       <c r="P38">
-        <v>1.241076600000001</v>
+        <v>1.215550950000001</v>
       </c>
       <c r="Q38">
-        <v>3.211076600000001</v>
+        <v>3.185550950000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1134045302913754</v>
+        <v>0.1142889432988502</v>
       </c>
       <c r="T38">
-        <v>1.355042218080847</v>
+        <v>1.372769091682114</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.350576772775621</v>
+        <v>2.287047670808712</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09303653427827564</v>
+        <v>0.09302816917007102</v>
       </c>
       <c r="C39">
-        <v>26.04462572428664</v>
+        <v>25.60172078782299</v>
       </c>
       <c r="D39">
-        <v>42.09962572428664</v>
+        <v>42.10572078782299</v>
       </c>
       <c r="E39">
-        <v>3.013</v>
+        <v>3.462000000000002</v>
       </c>
       <c r="F39">
-        <v>16.613</v>
+        <v>17.062</v>
       </c>
       <c r="G39">
         <v>0.5580000000000001</v>
@@ -4473,28 +4473,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M39">
-        <v>1.2592654</v>
+        <v>1.2932996</v>
       </c>
       <c r="N39">
-        <v>1.620734600000001</v>
+        <v>1.586700400000001</v>
       </c>
       <c r="O39">
-        <v>0.4051836500000002</v>
+        <v>0.3966751000000002</v>
       </c>
       <c r="P39">
-        <v>1.215550950000001</v>
+        <v>1.190025300000001</v>
       </c>
       <c r="Q39">
-        <v>3.185550950000001</v>
+        <v>3.1600253</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1142889432988502</v>
+        <v>0.1152018857581791</v>
       </c>
       <c r="T39">
-        <v>1.372769091682114</v>
+        <v>1.39106779991568</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.287047670808712</v>
+        <v>2.226862205787429</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09302816917007102</v>
+        <v>0.09301980406186641</v>
       </c>
       <c r="C40">
-        <v>25.60172078782299</v>
+        <v>25.15881761646665</v>
       </c>
       <c r="D40">
-        <v>42.10572078782299</v>
+        <v>42.11181761646665</v>
       </c>
       <c r="E40">
-        <v>3.462000000000002</v>
+        <v>3.911</v>
       </c>
       <c r="F40">
-        <v>17.062</v>
+        <v>17.511</v>
       </c>
       <c r="G40">
         <v>0.5580000000000001</v>
@@ -4555,28 +4555,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M40">
-        <v>1.2932996</v>
+        <v>1.3273338</v>
       </c>
       <c r="N40">
-        <v>1.586700400000001</v>
+        <v>1.552666200000001</v>
       </c>
       <c r="O40">
-        <v>0.3966751000000002</v>
+        <v>0.3881665500000002</v>
       </c>
       <c r="P40">
-        <v>1.190025300000001</v>
+        <v>1.16449965</v>
       </c>
       <c r="Q40">
-        <v>3.1600253</v>
+        <v>3.13449965</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1152018857581791</v>
+        <v>0.116144760757158</v>
       </c>
       <c r="T40">
-        <v>1.39106779991568</v>
+        <v>1.409966465796248</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.226862205787429</v>
+        <v>2.169763174869804</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09301980406186641</v>
+        <v>0.09301143895366179</v>
       </c>
       <c r="C41">
-        <v>25.15881761646665</v>
+        <v>24.7159162109845</v>
       </c>
       <c r="D41">
-        <v>42.11181761646665</v>
+        <v>42.1179162109845</v>
       </c>
       <c r="E41">
-        <v>3.911</v>
+        <v>4.360000000000001</v>
       </c>
       <c r="F41">
-        <v>17.511</v>
+        <v>17.96</v>
       </c>
       <c r="G41">
         <v>0.5580000000000001</v>
@@ -4637,28 +4637,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M41">
-        <v>1.3273338</v>
+        <v>1.361368</v>
       </c>
       <c r="N41">
-        <v>1.552666200000001</v>
+        <v>1.518632000000001</v>
       </c>
       <c r="O41">
-        <v>0.3881665500000002</v>
+        <v>0.3796580000000002</v>
       </c>
       <c r="P41">
-        <v>1.16449965</v>
+        <v>1.138974000000001</v>
       </c>
       <c r="Q41">
-        <v>3.13449965</v>
+        <v>3.108974000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.116144760757158</v>
+        <v>0.1171190649227696</v>
       </c>
       <c r="T41">
-        <v>1.409966465796248</v>
+        <v>1.429495087206168</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.169763174869804</v>
+        <v>2.115519095498058</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09301143895366179</v>
+        <v>0.0930030738454572</v>
       </c>
       <c r="C42">
-        <v>24.7159162109845</v>
+        <v>24.27301657214382</v>
       </c>
       <c r="D42">
-        <v>42.1179162109845</v>
+        <v>42.12401657214382</v>
       </c>
       <c r="E42">
-        <v>4.360000000000001</v>
+        <v>4.809000000000003</v>
       </c>
       <c r="F42">
-        <v>17.96</v>
+        <v>18.409</v>
       </c>
       <c r="G42">
         <v>0.5580000000000001</v>
@@ -4719,28 +4719,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M42">
-        <v>1.361368</v>
+        <v>1.3954022</v>
       </c>
       <c r="N42">
-        <v>1.518632000000001</v>
+        <v>1.4845978</v>
       </c>
       <c r="O42">
-        <v>0.3796580000000002</v>
+        <v>0.3711494500000001</v>
       </c>
       <c r="P42">
-        <v>1.138974000000001</v>
+        <v>1.11344835</v>
       </c>
       <c r="Q42">
-        <v>3.108974000000001</v>
+        <v>3.08344835</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1171190649227696</v>
+        <v>0.1181263963482325</v>
       </c>
       <c r="T42">
-        <v>1.429495087206168</v>
+        <v>1.449685695782527</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.115519095498058</v>
+        <v>2.063921068778593</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0930030738454572</v>
+        <v>0.09299470873725256</v>
       </c>
       <c r="C43">
-        <v>24.27301657214382</v>
+        <v>23.83011870071241</v>
       </c>
       <c r="D43">
-        <v>42.12401657214382</v>
+        <v>42.13011870071242</v>
       </c>
       <c r="E43">
-        <v>4.809000000000003</v>
+        <v>5.258000000000001</v>
       </c>
       <c r="F43">
-        <v>18.409</v>
+        <v>18.858</v>
       </c>
       <c r="G43">
         <v>0.5580000000000001</v>
@@ -4801,28 +4801,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M43">
-        <v>1.3954022</v>
+        <v>1.4294364</v>
       </c>
       <c r="N43">
-        <v>1.4845978</v>
+        <v>1.450563600000001</v>
       </c>
       <c r="O43">
-        <v>0.3711494500000001</v>
+        <v>0.3626409000000002</v>
       </c>
       <c r="P43">
-        <v>1.11344835</v>
+        <v>1.0879227</v>
       </c>
       <c r="Q43">
-        <v>3.08344835</v>
+        <v>3.057922700000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1181263963482325</v>
+        <v>0.1191684633400906</v>
       </c>
       <c r="T43">
-        <v>1.449685695782527</v>
+        <v>1.470572532240828</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.063921068778593</v>
+        <v>2.014780090950532</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09299470873725257</v>
+        <v>0.09756584362904794</v>
       </c>
       <c r="C44">
-        <v>23.83011870071241</v>
+        <v>20.29074482824256</v>
       </c>
       <c r="D44">
-        <v>42.13011870071241</v>
+        <v>39.03974482824255</v>
       </c>
       <c r="E44">
-        <v>5.257999999999997</v>
+        <v>5.706999999999999</v>
       </c>
       <c r="F44">
-        <v>18.858</v>
+        <v>19.307</v>
       </c>
       <c r="G44">
         <v>0.5580000000000001</v>
@@ -4883,45 +4883,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M44">
-        <v>1.4294364</v>
+        <v>1.73763</v>
       </c>
       <c r="N44">
-        <v>1.450563600000001</v>
+        <v>1.142370000000001</v>
       </c>
       <c r="O44">
-        <v>0.3626409000000002</v>
+        <v>0.2855925000000002</v>
       </c>
       <c r="P44">
-        <v>1.087922700000001</v>
+        <v>0.8567775000000007</v>
       </c>
       <c r="Q44">
-        <v>3.057922700000001</v>
+        <v>2.826777500000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1191684633400906</v>
+        <v>0.120247094086049</v>
       </c>
       <c r="T44">
-        <v>1.470572532240828</v>
+        <v>1.492192240153807</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.014780090950532</v>
+        <v>1.657429947687368</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09756584362904794</v>
+        <v>0.09766397852084335</v>
       </c>
       <c r="C45">
-        <v>20.29074482824256</v>
+        <v>19.78036278444536</v>
       </c>
       <c r="D45">
-        <v>39.03974482824255</v>
+        <v>38.97836278444536</v>
       </c>
       <c r="E45">
-        <v>5.706999999999999</v>
+        <v>6.156000000000001</v>
       </c>
       <c r="F45">
-        <v>19.307</v>
+        <v>19.756</v>
       </c>
       <c r="G45">
         <v>0.5580000000000001</v>
@@ -4965,28 +4965,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M45">
-        <v>1.73763</v>
+        <v>1.77804</v>
       </c>
       <c r="N45">
-        <v>1.142370000000001</v>
+        <v>1.101960000000001</v>
       </c>
       <c r="O45">
-        <v>0.2855925000000002</v>
+        <v>0.2754900000000002</v>
       </c>
       <c r="P45">
-        <v>0.8567775000000007</v>
+        <v>0.8264700000000005</v>
       </c>
       <c r="Q45">
-        <v>2.826777500000001</v>
+        <v>2.79647</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.120247094086049</v>
+        <v>0.1213642473586488</v>
       </c>
       <c r="T45">
-        <v>1.492192240153807</v>
+        <v>1.51458408049225</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.657429947687368</v>
+        <v>1.619761085239928</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09766397852084335</v>
+        <v>0.09776211341263871</v>
       </c>
       <c r="C46">
-        <v>19.78036278444536</v>
+        <v>19.27017345915029</v>
       </c>
       <c r="D46">
-        <v>38.97836278444536</v>
+        <v>38.91717345915029</v>
       </c>
       <c r="E46">
-        <v>6.156000000000001</v>
+        <v>6.604999999999999</v>
       </c>
       <c r="F46">
-        <v>19.756</v>
+        <v>20.205</v>
       </c>
       <c r="G46">
         <v>0.5580000000000001</v>
@@ -5047,28 +5047,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M46">
-        <v>1.77804</v>
+        <v>1.81845</v>
       </c>
       <c r="N46">
-        <v>1.101960000000001</v>
+        <v>1.061550000000001</v>
       </c>
       <c r="O46">
-        <v>0.2754900000000002</v>
+        <v>0.2653875000000003</v>
       </c>
       <c r="P46">
-        <v>0.8264700000000005</v>
+        <v>0.7961625000000008</v>
       </c>
       <c r="Q46">
-        <v>2.79647</v>
+        <v>2.766162500000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1213642473586488</v>
+        <v>0.1225220243866158</v>
       </c>
       <c r="T46">
-        <v>1.51458408049225</v>
+        <v>1.537790169570272</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.619761085239928</v>
+        <v>1.583766394456818</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09776211341263871</v>
+        <v>0.0978602483044341</v>
       </c>
       <c r="C47">
-        <v>19.27017345915029</v>
+        <v>18.76017594617518</v>
       </c>
       <c r="D47">
-        <v>38.91717345915029</v>
+        <v>38.85617594617518</v>
       </c>
       <c r="E47">
-        <v>6.604999999999999</v>
+        <v>7.054</v>
       </c>
       <c r="F47">
-        <v>20.205</v>
+        <v>20.654</v>
       </c>
       <c r="G47">
         <v>0.5580000000000001</v>
@@ -5129,28 +5129,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M47">
-        <v>1.81845</v>
+        <v>1.85886</v>
       </c>
       <c r="N47">
-        <v>1.061550000000001</v>
+        <v>1.021140000000001</v>
       </c>
       <c r="O47">
-        <v>0.2653875000000003</v>
+        <v>0.2552850000000002</v>
       </c>
       <c r="P47">
-        <v>0.7961625000000008</v>
+        <v>0.7658550000000006</v>
       </c>
       <c r="Q47">
-        <v>2.766162500000001</v>
+        <v>2.735855000000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1225220243866158</v>
+        <v>0.1237226820452483</v>
       </c>
       <c r="T47">
-        <v>1.537790169570272</v>
+        <v>1.561855743428961</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.583766394456818</v>
+        <v>1.549336690229496</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0978602483044341</v>
+        <v>0.09795838319622947</v>
       </c>
       <c r="C48">
-        <v>18.76017594617518</v>
+        <v>18.25036934501025</v>
       </c>
       <c r="D48">
-        <v>38.85617594617518</v>
+        <v>38.79536934501025</v>
       </c>
       <c r="E48">
-        <v>7.054</v>
+        <v>7.503000000000002</v>
       </c>
       <c r="F48">
-        <v>20.654</v>
+        <v>21.103</v>
       </c>
       <c r="G48">
         <v>0.5580000000000001</v>
@@ -5211,28 +5211,28 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M48">
-        <v>1.85886</v>
+        <v>1.89927</v>
       </c>
       <c r="N48">
-        <v>1.021140000000001</v>
+        <v>0.9807300000000008</v>
       </c>
       <c r="O48">
-        <v>0.2552850000000002</v>
+        <v>0.2451825000000002</v>
       </c>
       <c r="P48">
-        <v>0.7658550000000006</v>
+        <v>0.7355475000000006</v>
       </c>
       <c r="Q48">
-        <v>2.735855000000001</v>
+        <v>2.705547500000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1237226820452483</v>
+        <v>0.1249686475400556</v>
       </c>
       <c r="T48">
-        <v>1.561855743428961</v>
+        <v>1.586829452150243</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.549336690229496</v>
+        <v>1.516372079799081</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09795838319622947</v>
+        <v>0.1205967369876702</v>
       </c>
       <c r="C49">
-        <v>18.25036934501025</v>
+        <v>7.510962584632427</v>
       </c>
       <c r="D49">
-        <v>38.79536934501025</v>
+        <v>28.50496258463243</v>
       </c>
       <c r="E49">
-        <v>7.503000000000002</v>
+        <v>7.952</v>
       </c>
       <c r="F49">
-        <v>21.103</v>
+        <v>21.552</v>
       </c>
       <c r="G49">
         <v>0.5580000000000001</v>
@@ -5293,45 +5293,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M49">
-        <v>1.89927</v>
+        <v>3.1638336</v>
       </c>
       <c r="N49">
-        <v>0.9807300000000008</v>
+        <v>-0.2838335999999995</v>
       </c>
       <c r="O49">
-        <v>0.2451825000000002</v>
+        <v>-0.07095839999999987</v>
       </c>
       <c r="P49">
-        <v>0.7355475000000006</v>
+        <v>-0.2128751999999996</v>
       </c>
       <c r="Q49">
-        <v>2.705547500000001</v>
+        <v>1.7571248</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1249686475400556</v>
+        <v>0.1272468687145106</v>
       </c>
       <c r="T49">
-        <v>1.586829452150243</v>
+        <v>1.632493342723951</v>
       </c>
       <c r="U49">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.25</v>
+        <v>0.2275720189582664</v>
       </c>
       <c r="W49">
-        <v>0.0675</v>
+        <v>0.1133924276169265</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.516372079799081</v>
+        <v>0.9102880758330655</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1205967369876702</v>
+        <v>0.1216067369876702</v>
       </c>
       <c r="C50">
-        <v>7.510962584632434</v>
+        <v>6.728581913435328</v>
       </c>
       <c r="D50">
-        <v>28.50496258463243</v>
+        <v>28.17158191343533</v>
       </c>
       <c r="E50">
-        <v>7.952</v>
+        <v>8.400999999999998</v>
       </c>
       <c r="F50">
-        <v>21.552</v>
+        <v>22.001</v>
       </c>
       <c r="G50">
         <v>0.5580000000000001</v>
@@ -5375,37 +5375,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M50">
-        <v>3.1638336</v>
+        <v>3.2297468</v>
       </c>
       <c r="N50">
-        <v>-0.2838335999999995</v>
+        <v>-0.3497467999999992</v>
       </c>
       <c r="O50">
-        <v>-0.07095839999999987</v>
+        <v>-0.08743669999999981</v>
       </c>
       <c r="P50">
-        <v>-0.2128751999999996</v>
+        <v>-0.2623100999999994</v>
       </c>
       <c r="Q50">
-        <v>1.7571248</v>
+        <v>1.707689900000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1272468687145106</v>
+        <v>0.1288438661402853</v>
       </c>
       <c r="T50">
-        <v>1.632493342723951</v>
+        <v>1.664503016110694</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2275720189582664</v>
+        <v>0.2229276920407507</v>
       </c>
       <c r="W50">
-        <v>0.1133924276169265</v>
+        <v>0.1140742148084178</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9102880758330655</v>
+        <v>0.891710768163003</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1216067369876702</v>
+        <v>0.1226167369876702</v>
       </c>
       <c r="C51">
-        <v>6.728581913435328</v>
+        <v>5.953909221225917</v>
       </c>
       <c r="D51">
-        <v>28.17158191343533</v>
+        <v>27.84590922122592</v>
       </c>
       <c r="E51">
-        <v>8.400999999999998</v>
+        <v>8.85</v>
       </c>
       <c r="F51">
-        <v>22.001</v>
+        <v>22.45</v>
       </c>
       <c r="G51">
         <v>0.5580000000000001</v>
@@ -5457,37 +5457,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M51">
-        <v>3.2297468</v>
+        <v>3.29566</v>
       </c>
       <c r="N51">
-        <v>-0.3497467999999992</v>
+        <v>-0.4156599999999995</v>
       </c>
       <c r="O51">
-        <v>-0.08743669999999981</v>
+        <v>-0.1039149999999999</v>
       </c>
       <c r="P51">
-        <v>-0.2623100999999994</v>
+        <v>-0.3117449999999996</v>
       </c>
       <c r="Q51">
-        <v>1.707689900000001</v>
+        <v>1.658255</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1288438661402853</v>
+        <v>0.130504743463091</v>
       </c>
       <c r="T51">
-        <v>1.664503016110694</v>
+        <v>1.697793076432908</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2229276920407507</v>
+        <v>0.2184691381999357</v>
       </c>
       <c r="W51">
-        <v>0.1140742148084178</v>
+        <v>0.1147287305122494</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.891710768163003</v>
+        <v>0.8738765527997429</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1226167369876702</v>
+        <v>0.1236267369876702</v>
       </c>
       <c r="C52">
-        <v>5.953909221225917</v>
+        <v>5.186680242729889</v>
       </c>
       <c r="D52">
-        <v>27.84590922122592</v>
+        <v>27.52768024272989</v>
       </c>
       <c r="E52">
-        <v>8.85</v>
+        <v>9.299000000000001</v>
       </c>
       <c r="F52">
-        <v>22.45</v>
+        <v>22.899</v>
       </c>
       <c r="G52">
         <v>0.5580000000000001</v>
@@ -5539,37 +5539,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M52">
-        <v>3.29566</v>
+        <v>3.3615732</v>
       </c>
       <c r="N52">
-        <v>-0.4156599999999995</v>
+        <v>-0.4815731999999997</v>
       </c>
       <c r="O52">
-        <v>-0.1039149999999999</v>
+        <v>-0.1203932999999999</v>
       </c>
       <c r="P52">
-        <v>-0.3117449999999996</v>
+        <v>-0.3611798999999998</v>
       </c>
       <c r="Q52">
-        <v>1.658255</v>
+        <v>1.6088201</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.130504743463091</v>
+        <v>0.1322334116970316</v>
       </c>
       <c r="T52">
-        <v>1.697793076432908</v>
+        <v>1.732441914727457</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2184691381999357</v>
+        <v>0.2141854296077801</v>
       </c>
       <c r="W52">
-        <v>0.1147287305122494</v>
+        <v>0.1153575789335779</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8738765527997429</v>
+        <v>0.8567417184311203</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1236267369876702</v>
+        <v>0.1246367369876702</v>
       </c>
       <c r="C53">
-        <v>5.186680242729889</v>
+        <v>4.426642656495638</v>
       </c>
       <c r="D53">
-        <v>27.52768024272989</v>
+        <v>27.21664265649564</v>
       </c>
       <c r="E53">
-        <v>9.299000000000001</v>
+        <v>9.747999999999999</v>
       </c>
       <c r="F53">
-        <v>22.899</v>
+        <v>23.348</v>
       </c>
       <c r="G53">
         <v>0.5580000000000001</v>
@@ -5621,37 +5621,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M53">
-        <v>3.3615732</v>
+        <v>3.4274864</v>
       </c>
       <c r="N53">
-        <v>-0.4815731999999997</v>
+        <v>-0.5474863999999995</v>
       </c>
       <c r="O53">
-        <v>-0.1203932999999999</v>
+        <v>-0.1368715999999999</v>
       </c>
       <c r="P53">
-        <v>-0.3611798999999998</v>
+        <v>-0.4106147999999996</v>
       </c>
       <c r="Q53">
-        <v>1.6088201</v>
+        <v>1.5593852</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1322334116970316</v>
+        <v>0.1340341077740532</v>
       </c>
       <c r="T53">
-        <v>1.732441914727457</v>
+        <v>1.768534454617613</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2141854296077801</v>
+        <v>0.2100664790383997</v>
       </c>
       <c r="W53">
-        <v>0.1153575789335779</v>
+        <v>0.1159622408771629</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8567417184311203</v>
+        <v>0.8402659161535989</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1246367369876702</v>
+        <v>0.1256467369876702</v>
       </c>
       <c r="C54">
-        <v>4.426642656495638</v>
+        <v>3.673555417662076</v>
       </c>
       <c r="D54">
-        <v>27.21664265649564</v>
+        <v>26.91255541766208</v>
       </c>
       <c r="E54">
-        <v>9.747999999999999</v>
+        <v>10.197</v>
       </c>
       <c r="F54">
-        <v>23.348</v>
+        <v>23.797</v>
       </c>
       <c r="G54">
         <v>0.5580000000000001</v>
@@ -5703,37 +5703,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M54">
-        <v>3.4274864</v>
+        <v>3.4933996</v>
       </c>
       <c r="N54">
-        <v>-0.5474863999999995</v>
+        <v>-0.6133995999999997</v>
       </c>
       <c r="O54">
-        <v>-0.1368715999999999</v>
+        <v>-0.1533498999999999</v>
       </c>
       <c r="P54">
-        <v>-0.4106147999999996</v>
+        <v>-0.4600496999999998</v>
       </c>
       <c r="Q54">
-        <v>1.5593852</v>
+        <v>1.5099503</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1340341077740532</v>
+        <v>0.1359114292160543</v>
       </c>
       <c r="T54">
-        <v>1.768534454617613</v>
+        <v>1.806162847269052</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2100664790383997</v>
+        <v>0.2061029605659771</v>
       </c>
       <c r="W54">
-        <v>0.1159622408771629</v>
+        <v>0.1165440853889146</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8402659161535989</v>
+        <v>0.8244118422639083</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1256467369876702</v>
+        <v>0.1266567369876702</v>
       </c>
       <c r="C55">
-        <v>3.673555417662076</v>
+        <v>2.927188134961444</v>
       </c>
       <c r="D55">
-        <v>26.91255541766208</v>
+        <v>26.61518813496145</v>
       </c>
       <c r="E55">
-        <v>10.197</v>
+        <v>10.646</v>
       </c>
       <c r="F55">
-        <v>23.797</v>
+        <v>24.246</v>
       </c>
       <c r="G55">
         <v>0.5580000000000001</v>
@@ -5785,37 +5785,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M55">
-        <v>3.4933996</v>
+        <v>3.559312800000001</v>
       </c>
       <c r="N55">
-        <v>-0.6133995999999997</v>
+        <v>-0.6793127999999999</v>
       </c>
       <c r="O55">
-        <v>-0.1533498999999999</v>
+        <v>-0.1698282</v>
       </c>
       <c r="P55">
-        <v>-0.4600496999999998</v>
+        <v>-0.5094846</v>
       </c>
       <c r="Q55">
-        <v>1.5099503</v>
+        <v>1.4605154</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1359114292160543</v>
+        <v>0.1378703733294468</v>
       </c>
       <c r="T55">
-        <v>1.806162847269052</v>
+        <v>1.845427256992292</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2061029605659771</v>
+        <v>0.2022862390740145</v>
       </c>
       <c r="W55">
-        <v>0.1165440853889146</v>
+        <v>0.1171043801039347</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8244118422639083</v>
+        <v>0.8091449562960581</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1266567369876702</v>
+        <v>0.1587634414882492</v>
       </c>
       <c r="C56">
-        <v>2.927188134961444</v>
+        <v>-4.440239569728163</v>
       </c>
       <c r="D56">
-        <v>26.61518813496145</v>
+        <v>19.69676043027184</v>
       </c>
       <c r="E56">
-        <v>10.646</v>
+        <v>11.095</v>
       </c>
       <c r="F56">
-        <v>24.246</v>
+        <v>24.695</v>
       </c>
       <c r="G56">
         <v>0.5580000000000001</v>
@@ -5867,45 +5867,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M56">
-        <v>3.559312800000001</v>
+        <v>4.958756</v>
       </c>
       <c r="N56">
-        <v>-0.6793127999999999</v>
+        <v>-2.078755999999999</v>
       </c>
       <c r="O56">
-        <v>-0.1698282</v>
+        <v>-0.5196889999999998</v>
       </c>
       <c r="P56">
-        <v>-0.5094846</v>
+        <v>-1.559067</v>
       </c>
       <c r="Q56">
-        <v>1.4605154</v>
+        <v>0.4109330000000004</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1378703733294468</v>
+        <v>0.143020169404721</v>
       </c>
       <c r="T56">
-        <v>1.845427256992292</v>
+        <v>1.948648018477175</v>
       </c>
       <c r="U56">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.2022862390740145</v>
+        <v>0.1451977068442166</v>
       </c>
       <c r="W56">
-        <v>0.1171043801039347</v>
+        <v>0.1716443004656813</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8091449562960581</v>
+        <v>0.5807908273768665</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1587634414882492</v>
+        <v>0.1603134414882492</v>
       </c>
       <c r="C57">
-        <v>-4.440239569728163</v>
+        <v>-5.133353480900446</v>
       </c>
       <c r="D57">
-        <v>19.69676043027184</v>
+        <v>19.45264651909956</v>
       </c>
       <c r="E57">
-        <v>11.095</v>
+        <v>11.544</v>
       </c>
       <c r="F57">
-        <v>24.695</v>
+        <v>25.144</v>
       </c>
       <c r="G57">
         <v>0.5580000000000001</v>
@@ -5949,37 +5949,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M57">
-        <v>4.958756</v>
+        <v>5.048915200000001</v>
       </c>
       <c r="N57">
-        <v>-2.078755999999999</v>
+        <v>-2.1689152</v>
       </c>
       <c r="O57">
-        <v>-0.5196889999999998</v>
+        <v>-0.5422288</v>
       </c>
       <c r="P57">
-        <v>-1.559067</v>
+        <v>-1.6266864</v>
       </c>
       <c r="Q57">
-        <v>0.4109330000000004</v>
+        <v>0.3433136000000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.143020169404721</v>
+        <v>0.1452297187093738</v>
       </c>
       <c r="T57">
-        <v>1.948648018477175</v>
+        <v>1.992935473442565</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1451977068442166</v>
+        <v>0.1426048906505699</v>
       </c>
       <c r="W57">
-        <v>0.1716443004656813</v>
+        <v>0.1721649379573656</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5807908273768665</v>
+        <v>0.5704195626022794</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1603134414882492</v>
+        <v>0.1618634414882492</v>
       </c>
       <c r="C58">
-        <v>-5.133353480900446</v>
+        <v>-5.820490562711338</v>
       </c>
       <c r="D58">
-        <v>19.45264651909956</v>
+        <v>19.21450943728867</v>
       </c>
       <c r="E58">
-        <v>11.544</v>
+        <v>11.993</v>
       </c>
       <c r="F58">
-        <v>25.144</v>
+        <v>25.593</v>
       </c>
       <c r="G58">
         <v>0.5580000000000001</v>
@@ -6031,37 +6031,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M58">
-        <v>5.048915200000001</v>
+        <v>5.139074400000001</v>
       </c>
       <c r="N58">
-        <v>-2.1689152</v>
+        <v>-2.2590744</v>
       </c>
       <c r="O58">
-        <v>-0.5422288</v>
+        <v>-0.5647686000000001</v>
       </c>
       <c r="P58">
-        <v>-1.6266864</v>
+        <v>-1.6943058</v>
       </c>
       <c r="Q58">
-        <v>0.3433136000000001</v>
+        <v>0.2756941999999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1452297187093738</v>
+        <v>0.1475420377491266</v>
       </c>
       <c r="T58">
-        <v>1.992935473442565</v>
+        <v>2.039282810034253</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1426048906505699</v>
+        <v>0.1401030504637178</v>
       </c>
       <c r="W58">
-        <v>0.1721649379573656</v>
+        <v>0.1726673074668855</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5704195626022794</v>
+        <v>0.560412201854871</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1618634414882492</v>
+        <v>0.1634134414882492</v>
       </c>
       <c r="C59">
-        <v>-5.820490562711338</v>
+        <v>-6.501867663519665</v>
       </c>
       <c r="D59">
-        <v>19.21450943728867</v>
+        <v>18.98213233648034</v>
       </c>
       <c r="E59">
-        <v>11.993</v>
+        <v>12.442</v>
       </c>
       <c r="F59">
-        <v>25.593</v>
+        <v>26.042</v>
       </c>
       <c r="G59">
         <v>0.5580000000000001</v>
@@ -6113,37 +6113,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M59">
-        <v>5.139074400000001</v>
+        <v>5.229233600000001</v>
       </c>
       <c r="N59">
-        <v>-2.2590744</v>
+        <v>-2.3492336</v>
       </c>
       <c r="O59">
-        <v>-0.5647686000000001</v>
+        <v>-0.5873084</v>
       </c>
       <c r="P59">
-        <v>-1.6943058</v>
+        <v>-1.7619252</v>
       </c>
       <c r="Q59">
-        <v>0.2756941999999998</v>
+        <v>0.2080748000000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1475420377491266</v>
+        <v>0.1499644672193439</v>
       </c>
       <c r="T59">
-        <v>2.039282810034253</v>
+        <v>2.087837162654116</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1401030504637178</v>
+        <v>0.1376874806281364</v>
       </c>
       <c r="W59">
-        <v>0.1726673074668855</v>
+        <v>0.1731523538898702</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.560412201854871</v>
+        <v>0.5507499225125457</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1634134414882492</v>
+        <v>0.1649634414882492</v>
       </c>
       <c r="C60">
-        <v>-6.501867663519661</v>
+        <v>-7.177691266921158</v>
       </c>
       <c r="D60">
-        <v>18.98213233648034</v>
+        <v>18.75530873307884</v>
       </c>
       <c r="E60">
-        <v>12.442</v>
+        <v>12.891</v>
       </c>
       <c r="F60">
-        <v>26.042</v>
+        <v>26.491</v>
       </c>
       <c r="G60">
         <v>0.5580000000000001</v>
@@ -6195,37 +6195,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M60">
-        <v>5.2292336</v>
+        <v>5.319392799999999</v>
       </c>
       <c r="N60">
-        <v>-2.349233599999999</v>
+        <v>-2.439392799999998</v>
       </c>
       <c r="O60">
-        <v>-0.5873083999999997</v>
+        <v>-0.6098481999999996</v>
       </c>
       <c r="P60">
-        <v>-1.761925199999999</v>
+        <v>-1.829544599999999</v>
       </c>
       <c r="Q60">
-        <v>0.2080748000000008</v>
+        <v>0.1404554000000011</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1499644672193439</v>
+        <v>0.1525050639807913</v>
       </c>
       <c r="T60">
-        <v>2.087837162654115</v>
+        <v>2.138760020279826</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1376874806281365</v>
+        <v>0.1353537945157952</v>
       </c>
       <c r="W60">
-        <v>0.1731523538898702</v>
+        <v>0.1736209580612283</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5507499225125458</v>
+        <v>0.5414151780631806</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1649634414882492</v>
+        <v>0.1665134414882491</v>
       </c>
       <c r="C61">
-        <v>-7.177691266921158</v>
+        <v>-7.848158103695571</v>
       </c>
       <c r="D61">
-        <v>18.75530873307884</v>
+        <v>18.53384189630443</v>
       </c>
       <c r="E61">
-        <v>12.891</v>
+        <v>13.34</v>
       </c>
       <c r="F61">
-        <v>26.491</v>
+        <v>26.94</v>
       </c>
       <c r="G61">
         <v>0.5580000000000001</v>
@@ -6277,37 +6277,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M61">
-        <v>5.319392799999999</v>
+        <v>5.409552</v>
       </c>
       <c r="N61">
-        <v>-2.439392799999998</v>
+        <v>-2.529551999999999</v>
       </c>
       <c r="O61">
-        <v>-0.6098481999999996</v>
+        <v>-0.6323879999999997</v>
       </c>
       <c r="P61">
-        <v>-1.829544599999999</v>
+        <v>-1.897163999999999</v>
       </c>
       <c r="Q61">
-        <v>0.1404554000000011</v>
+        <v>0.07283600000000079</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1525050639807913</v>
+        <v>0.1551726905803111</v>
       </c>
       <c r="T61">
-        <v>2.138760020279826</v>
+        <v>2.192229020786822</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1353537945157952</v>
+        <v>0.1330978979405319</v>
       </c>
       <c r="W61">
-        <v>0.1736209580612283</v>
+        <v>0.1740739420935412</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5414151780631806</v>
+        <v>0.5323915917621276</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1665134414882491</v>
+        <v>0.1680634414882492</v>
       </c>
       <c r="C62">
-        <v>-7.848158103695571</v>
+        <v>-8.513455720903639</v>
       </c>
       <c r="D62">
-        <v>18.53384189630443</v>
+        <v>18.31754427909636</v>
       </c>
       <c r="E62">
-        <v>13.34</v>
+        <v>13.789</v>
       </c>
       <c r="F62">
-        <v>26.94</v>
+        <v>27.389</v>
       </c>
       <c r="G62">
         <v>0.5580000000000001</v>
@@ -6359,37 +6359,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M62">
-        <v>5.409552</v>
+        <v>5.4997112</v>
       </c>
       <c r="N62">
-        <v>-2.529551999999999</v>
+        <v>-2.619711199999999</v>
       </c>
       <c r="O62">
-        <v>-0.6323879999999997</v>
+        <v>-0.6549277999999998</v>
       </c>
       <c r="P62">
-        <v>-1.897163999999999</v>
+        <v>-1.9647834</v>
       </c>
       <c r="Q62">
-        <v>0.07283600000000079</v>
+        <v>0.00521660000000046</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1551726905803111</v>
+        <v>0.1579771185439089</v>
       </c>
       <c r="T62">
-        <v>2.192229020786822</v>
+        <v>2.248440021319817</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1330978979405319</v>
+        <v>0.1309159651874084</v>
       </c>
       <c r="W62">
-        <v>0.1740739420935412</v>
+        <v>0.1745120741903684</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5323915917621276</v>
+        <v>0.5236638607496337</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1680634414882492</v>
+        <v>0.1696134414882492</v>
       </c>
       <c r="C63">
-        <v>-8.513455720903639</v>
+        <v>-9.173763011594282</v>
       </c>
       <c r="D63">
-        <v>18.31754427909636</v>
+        <v>18.10623698840572</v>
       </c>
       <c r="E63">
-        <v>13.789</v>
+        <v>14.238</v>
       </c>
       <c r="F63">
-        <v>27.389</v>
+        <v>27.838</v>
       </c>
       <c r="G63">
         <v>0.5580000000000001</v>
@@ -6441,37 +6441,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M63">
-        <v>5.4997112</v>
+        <v>5.5898704</v>
       </c>
       <c r="N63">
-        <v>-2.619711199999999</v>
+        <v>-2.709870399999999</v>
       </c>
       <c r="O63">
-        <v>-0.6549277999999998</v>
+        <v>-0.6774675999999997</v>
       </c>
       <c r="P63">
-        <v>-1.9647834</v>
+        <v>-2.032402799999999</v>
       </c>
       <c r="Q63">
-        <v>0.00521660000000046</v>
+        <v>-0.06240279999999898</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1579771185439089</v>
+        <v>0.1609291479792749</v>
       </c>
       <c r="T63">
-        <v>2.248440021319817</v>
+        <v>2.307609495565076</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1309159651874084</v>
+        <v>0.1288044173618051</v>
       </c>
       <c r="W63">
-        <v>0.1745120741903684</v>
+        <v>0.1749360729937496</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5236638607496337</v>
+        <v>0.5152176694472203</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1696134414882492</v>
+        <v>0.1711634414882492</v>
       </c>
       <c r="C64">
-        <v>-9.173763011594282</v>
+        <v>-9.829250708266276</v>
       </c>
       <c r="D64">
-        <v>18.10623698840572</v>
+        <v>17.89974929173372</v>
       </c>
       <c r="E64">
-        <v>14.238</v>
+        <v>14.687</v>
       </c>
       <c r="F64">
-        <v>27.838</v>
+        <v>28.287</v>
       </c>
       <c r="G64">
         <v>0.5580000000000001</v>
@@ -6523,37 +6523,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M64">
-        <v>5.5898704</v>
+        <v>5.6800296</v>
       </c>
       <c r="N64">
-        <v>-2.709870399999999</v>
+        <v>-2.800029599999999</v>
       </c>
       <c r="O64">
-        <v>-0.6774675999999997</v>
+        <v>-0.7000073999999998</v>
       </c>
       <c r="P64">
-        <v>-2.032402799999999</v>
+        <v>-2.1000222</v>
       </c>
       <c r="Q64">
-        <v>-0.06240279999999898</v>
+        <v>-0.1300221999999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1609291479792749</v>
+        <v>0.1640407465733093</v>
       </c>
       <c r="T64">
-        <v>2.307609495565076</v>
+        <v>2.369977319769537</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1288044173618051</v>
+        <v>0.1267599028005066</v>
       </c>
       <c r="W64">
-        <v>0.1749360729937496</v>
+        <v>0.1753466115176583</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5152176694472203</v>
+        <v>0.5070396112020262</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1711634414882492</v>
+        <v>0.1956770286245523</v>
       </c>
       <c r="C65">
-        <v>-9.829250708266276</v>
+        <v>-13.01335236220939</v>
       </c>
       <c r="D65">
-        <v>17.89974929173372</v>
+        <v>15.16464763779062</v>
       </c>
       <c r="E65">
-        <v>14.687</v>
+        <v>15.136</v>
       </c>
       <c r="F65">
-        <v>28.287</v>
+        <v>28.736</v>
       </c>
       <c r="G65">
         <v>0.5580000000000001</v>
@@ -6605,45 +6605,45 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M65">
-        <v>5.6800296</v>
+        <v>6.7759488</v>
       </c>
       <c r="N65">
-        <v>-2.800029599999999</v>
+        <v>-3.895948799999999</v>
       </c>
       <c r="O65">
-        <v>-0.7000073999999998</v>
+        <v>-0.9739871999999998</v>
       </c>
       <c r="P65">
-        <v>-2.1000222</v>
+        <v>-2.921961599999999</v>
       </c>
       <c r="Q65">
-        <v>-0.1300221999999998</v>
+        <v>-0.9519615999999995</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1640407465733093</v>
+        <v>0.1688907315789654</v>
       </c>
       <c r="T65">
-        <v>2.369977319769537</v>
+        <v>2.467188770117584</v>
       </c>
       <c r="U65">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1267599028005066</v>
+        <v>0.1062581818800048</v>
       </c>
       <c r="W65">
-        <v>0.1753466115176583</v>
+        <v>0.2107443207126949</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5070396112020262</v>
+        <v>0.4250327275200192</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1956770286245523</v>
+        <v>0.1975770286245523</v>
       </c>
       <c r="C66">
-        <v>-13.01335236220939</v>
+        <v>-13.63984989252041</v>
       </c>
       <c r="D66">
-        <v>15.16464763779062</v>
+        <v>14.98715010747959</v>
       </c>
       <c r="E66">
-        <v>15.136</v>
+        <v>15.585</v>
       </c>
       <c r="F66">
-        <v>28.736</v>
+        <v>29.185</v>
       </c>
       <c r="G66">
         <v>0.5580000000000001</v>
@@ -6687,37 +6687,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M66">
-        <v>6.7759488</v>
+        <v>6.881823</v>
       </c>
       <c r="N66">
-        <v>-3.895948799999999</v>
+        <v>-4.001822999999999</v>
       </c>
       <c r="O66">
-        <v>-0.9739871999999998</v>
+        <v>-1.00045575</v>
       </c>
       <c r="P66">
-        <v>-2.921961599999999</v>
+        <v>-3.001367249999999</v>
       </c>
       <c r="Q66">
-        <v>-0.9519615999999995</v>
+        <v>-1.03136725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1688907315789654</v>
+        <v>0.1724076096240787</v>
       </c>
       <c r="T66">
-        <v>2.467188770117584</v>
+        <v>2.537679877835229</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1062581818800048</v>
+        <v>0.1046234406203124</v>
       </c>
       <c r="W66">
-        <v>0.2107443207126949</v>
+        <v>0.2111297927017304</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4250327275200192</v>
+        <v>0.4184937624812497</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1975770286245523</v>
+        <v>0.1994770286245523</v>
       </c>
       <c r="C67">
-        <v>-13.63984989252041</v>
+        <v>-14.26224038657004</v>
       </c>
       <c r="D67">
-        <v>14.98715010747959</v>
+        <v>14.81375961342996</v>
       </c>
       <c r="E67">
-        <v>15.585</v>
+        <v>16.034</v>
       </c>
       <c r="F67">
-        <v>29.185</v>
+        <v>29.634</v>
       </c>
       <c r="G67">
         <v>0.5580000000000001</v>
@@ -6769,37 +6769,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M67">
-        <v>6.881823</v>
+        <v>6.9876972</v>
       </c>
       <c r="N67">
-        <v>-4.001822999999999</v>
+        <v>-4.1076972</v>
       </c>
       <c r="O67">
-        <v>-1.00045575</v>
+        <v>-1.0269243</v>
       </c>
       <c r="P67">
-        <v>-3.001367249999999</v>
+        <v>-3.080772899999999</v>
       </c>
       <c r="Q67">
-        <v>-1.03136725</v>
+        <v>-1.1107729</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1724076096240787</v>
+        <v>0.1761313628483163</v>
       </c>
       <c r="T67">
-        <v>2.537679877835229</v>
+        <v>2.612317521300971</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1046234406203124</v>
+        <v>0.1030382369745501</v>
       </c>
       <c r="W67">
-        <v>0.2111297927017304</v>
+        <v>0.2115035837214011</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4184937624812497</v>
+        <v>0.4121529478982003</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1994770286245523</v>
+        <v>0.2013770286245523</v>
       </c>
       <c r="C68">
-        <v>-14.26224038657004</v>
+        <v>-14.88066476038465</v>
       </c>
       <c r="D68">
-        <v>14.81375961342996</v>
+        <v>14.64433523961535</v>
       </c>
       <c r="E68">
-        <v>16.034</v>
+        <v>16.483</v>
       </c>
       <c r="F68">
-        <v>29.634</v>
+        <v>30.083</v>
       </c>
       <c r="G68">
         <v>0.5580000000000001</v>
@@ -6851,37 +6851,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M68">
-        <v>6.9876972</v>
+        <v>7.093571400000001</v>
       </c>
       <c r="N68">
-        <v>-4.1076972</v>
+        <v>-4.2135714</v>
       </c>
       <c r="O68">
-        <v>-1.0269243</v>
+        <v>-1.05339285</v>
       </c>
       <c r="P68">
-        <v>-3.080772899999999</v>
+        <v>-3.16017855</v>
       </c>
       <c r="Q68">
-        <v>-1.1107729</v>
+        <v>-1.19017855</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1761313628483163</v>
+        <v>0.1800807980861441</v>
       </c>
       <c r="T68">
-        <v>2.612317521300971</v>
+        <v>2.691478658310091</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1030382369745501</v>
+        <v>0.1015003528406016</v>
       </c>
       <c r="W68">
-        <v>0.2115035837214011</v>
+        <v>0.2118662168001862</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4121529478982003</v>
+        <v>0.4060014113624063</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2013770286245523</v>
+        <v>0.2032770286245523</v>
       </c>
       <c r="C69">
-        <v>-14.88066476038465</v>
+        <v>-15.49525755628273</v>
       </c>
       <c r="D69">
-        <v>14.64433523961535</v>
+        <v>14.47874244371727</v>
       </c>
       <c r="E69">
-        <v>16.483</v>
+        <v>16.932</v>
       </c>
       <c r="F69">
-        <v>30.083</v>
+        <v>30.532</v>
       </c>
       <c r="G69">
         <v>0.5580000000000001</v>
@@ -6933,37 +6933,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M69">
-        <v>7.093571400000001</v>
+        <v>7.199445600000001</v>
       </c>
       <c r="N69">
-        <v>-4.2135714</v>
+        <v>-4.3194456</v>
       </c>
       <c r="O69">
-        <v>-1.05339285</v>
+        <v>-1.0798614</v>
       </c>
       <c r="P69">
-        <v>-3.16017855</v>
+        <v>-3.2395842</v>
       </c>
       <c r="Q69">
-        <v>-1.19017855</v>
+        <v>-1.2695842</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1800807980861441</v>
+        <v>0.1842770730263361</v>
       </c>
       <c r="T69">
-        <v>2.691478658310091</v>
+        <v>2.775587366382283</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1015003528406016</v>
+        <v>0.1000077005929457</v>
       </c>
       <c r="W69">
-        <v>0.2118662168001862</v>
+        <v>0.2122181842001834</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4060014113624063</v>
+        <v>0.4000308023717827</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2032770286245523</v>
+        <v>0.2051770286245523</v>
       </c>
       <c r="C70">
-        <v>-15.49525755628273</v>
+        <v>-16.10614729920342</v>
       </c>
       <c r="D70">
-        <v>14.47874244371727</v>
+        <v>14.31685270079658</v>
       </c>
       <c r="E70">
-        <v>16.932</v>
+        <v>17.381</v>
       </c>
       <c r="F70">
-        <v>30.532</v>
+        <v>30.981</v>
       </c>
       <c r="G70">
         <v>0.5580000000000001</v>
@@ -7015,37 +7015,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M70">
-        <v>7.199445600000001</v>
+        <v>7.3053198</v>
       </c>
       <c r="N70">
-        <v>-4.3194456</v>
+        <v>-4.4253198</v>
       </c>
       <c r="O70">
-        <v>-1.0798614</v>
+        <v>-1.10632995</v>
       </c>
       <c r="P70">
-        <v>-3.2395842</v>
+        <v>-3.318989849999999</v>
       </c>
       <c r="Q70">
-        <v>-1.2695842</v>
+        <v>-1.348989849999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1842770730263361</v>
+        <v>0.1887440753820244</v>
       </c>
       <c r="T70">
-        <v>2.775587366382283</v>
+        <v>2.865122442717195</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1000077005929457</v>
+        <v>0.09855831362783052</v>
       </c>
       <c r="W70">
-        <v>0.2122181842001834</v>
+        <v>0.2125599496465576</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4000308023717827</v>
+        <v>0.3942332545113221</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2051770286245523</v>
+        <v>0.2070770286245523</v>
       </c>
       <c r="C71">
-        <v>-16.10614729920342</v>
+        <v>-16.71345682939439</v>
       </c>
       <c r="D71">
-        <v>14.31685270079658</v>
+        <v>14.15854317060561</v>
       </c>
       <c r="E71">
-        <v>17.381</v>
+        <v>17.83000000000001</v>
       </c>
       <c r="F71">
-        <v>30.981</v>
+        <v>31.43</v>
       </c>
       <c r="G71">
         <v>0.5580000000000001</v>
@@ -7097,37 +7097,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M71">
-        <v>7.3053198</v>
+        <v>7.411194000000001</v>
       </c>
       <c r="N71">
-        <v>-4.4253198</v>
+        <v>-4.531194</v>
       </c>
       <c r="O71">
-        <v>-1.10632995</v>
+        <v>-1.1327985</v>
       </c>
       <c r="P71">
-        <v>-3.318989849999999</v>
+        <v>-3.3983955</v>
       </c>
       <c r="Q71">
-        <v>-1.348989849999999</v>
+        <v>-1.4283955</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1887440753820244</v>
+        <v>0.1935088778947585</v>
       </c>
       <c r="T71">
-        <v>2.865122442717195</v>
+        <v>2.960626524141101</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09855831362783052</v>
+        <v>0.09715033771886152</v>
       </c>
       <c r="W71">
-        <v>0.2125599496465576</v>
+        <v>0.2128919503658925</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3942332545113221</v>
+        <v>0.388601350875446</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2070770286245523</v>
+        <v>0.2089770286245523</v>
       </c>
       <c r="C72">
-        <v>-16.71345682939439</v>
+        <v>-17.31730361326868</v>
       </c>
       <c r="D72">
-        <v>14.15854317060561</v>
+        <v>14.00369638673132</v>
       </c>
       <c r="E72">
-        <v>17.83000000000001</v>
+        <v>18.279</v>
       </c>
       <c r="F72">
-        <v>31.43</v>
+        <v>31.879</v>
       </c>
       <c r="G72">
         <v>0.5580000000000001</v>
@@ -7179,37 +7179,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M72">
-        <v>7.411194000000001</v>
+        <v>7.517068200000001</v>
       </c>
       <c r="N72">
-        <v>-4.531194</v>
+        <v>-4.6370682</v>
       </c>
       <c r="O72">
-        <v>-1.1327985</v>
+        <v>-1.15926705</v>
       </c>
       <c r="P72">
-        <v>-3.3983955</v>
+        <v>-3.47780115</v>
       </c>
       <c r="Q72">
-        <v>-1.4283955</v>
+        <v>-1.50780115</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1935088778947585</v>
+        <v>0.1986022874773364</v>
       </c>
       <c r="T72">
-        <v>2.960626524141101</v>
+        <v>3.06271709393907</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09715033771886152</v>
+        <v>0.0957820231031029</v>
       </c>
       <c r="W72">
-        <v>0.2128919503658925</v>
+        <v>0.2132145989522883</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.388601350875446</v>
+        <v>0.3831280924124116</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2089770286245523</v>
+        <v>0.2108770286245523</v>
       </c>
       <c r="C73">
-        <v>-17.31730361326868</v>
+        <v>-17.91780003408398</v>
       </c>
       <c r="D73">
-        <v>14.00369638673132</v>
+        <v>13.85219996591601</v>
       </c>
       <c r="E73">
-        <v>18.279</v>
+        <v>18.72799999999999</v>
       </c>
       <c r="F73">
-        <v>31.879</v>
+        <v>32.328</v>
       </c>
       <c r="G73">
         <v>0.5580000000000001</v>
@@ -7261,37 +7261,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M73">
-        <v>7.5170682</v>
+        <v>7.622942399999999</v>
       </c>
       <c r="N73">
-        <v>-4.637068199999999</v>
+        <v>-4.742942399999999</v>
       </c>
       <c r="O73">
-        <v>-1.15926705</v>
+        <v>-1.1857356</v>
       </c>
       <c r="P73">
-        <v>-3.477801149999999</v>
+        <v>-3.557206799999999</v>
       </c>
       <c r="Q73">
-        <v>-1.507801149999999</v>
+        <v>-1.587206799999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1986022874773364</v>
+        <v>0.2040595120300984</v>
       </c>
       <c r="T73">
-        <v>3.06271709393907</v>
+        <v>3.172099847294036</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09578202310310291</v>
+        <v>0.09445171722667094</v>
       </c>
       <c r="W73">
-        <v>0.2132145989522883</v>
+        <v>0.213528285077951</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3831280924124116</v>
+        <v>0.3778068689066837</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2108770286245523</v>
+        <v>0.2127770286245523</v>
       </c>
       <c r="C74">
-        <v>-17.91780003408398</v>
+        <v>-18.5150536639558</v>
       </c>
       <c r="D74">
-        <v>13.85219996591601</v>
+        <v>13.7039463360442</v>
       </c>
       <c r="E74">
-        <v>18.72799999999999</v>
+        <v>19.177</v>
       </c>
       <c r="F74">
-        <v>32.328</v>
+        <v>32.777</v>
       </c>
       <c r="G74">
         <v>0.5580000000000001</v>
@@ -7343,37 +7343,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M74">
-        <v>7.622942399999999</v>
+        <v>7.728816600000001</v>
       </c>
       <c r="N74">
-        <v>-4.742942399999999</v>
+        <v>-4.8488166</v>
       </c>
       <c r="O74">
-        <v>-1.1857356</v>
+        <v>-1.21220415</v>
       </c>
       <c r="P74">
-        <v>-3.557206799999999</v>
+        <v>-3.63661245</v>
       </c>
       <c r="Q74">
-        <v>-1.587206799999999</v>
+        <v>-1.66661245</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2040595120300984</v>
+        <v>0.2099209754386205</v>
       </c>
       <c r="T74">
-        <v>3.172099847294036</v>
+        <v>3.289585026823445</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09445171722667094</v>
+        <v>0.09315785808657953</v>
       </c>
       <c r="W74">
-        <v>0.213528285077951</v>
+        <v>0.2138333770631846</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3778068689066837</v>
+        <v>0.3726314323463181</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2127770286245523</v>
+        <v>0.2146770286245523</v>
       </c>
       <c r="C75">
-        <v>-18.5150536639558</v>
+        <v>-19.10916751858822</v>
       </c>
       <c r="D75">
-        <v>13.7039463360442</v>
+        <v>13.55883248141178</v>
       </c>
       <c r="E75">
-        <v>19.177</v>
+        <v>19.626</v>
       </c>
       <c r="F75">
-        <v>32.777</v>
+        <v>33.226</v>
       </c>
       <c r="G75">
         <v>0.5580000000000001</v>
@@ -7425,37 +7425,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M75">
-        <v>7.728816600000001</v>
+        <v>7.8346908</v>
       </c>
       <c r="N75">
-        <v>-4.8488166</v>
+        <v>-4.954690799999999</v>
       </c>
       <c r="O75">
-        <v>-1.21220415</v>
+        <v>-1.2386727</v>
       </c>
       <c r="P75">
-        <v>-3.63661245</v>
+        <v>-3.716018099999999</v>
       </c>
       <c r="Q75">
-        <v>-1.66661245</v>
+        <v>-1.746018099999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2099209754386205</v>
+        <v>0.2162333206477982</v>
       </c>
       <c r="T75">
-        <v>3.289585026823445</v>
+        <v>3.416107527855115</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09315785808657953</v>
+        <v>0.09189896811243657</v>
       </c>
       <c r="W75">
-        <v>0.2138333770631846</v>
+        <v>0.2141302233190875</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3726314323463181</v>
+        <v>0.3675958724497463</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2146770286245523</v>
+        <v>0.2165770286245522</v>
       </c>
       <c r="C76">
-        <v>-19.10916751858822</v>
+        <v>-19.70024029598993</v>
       </c>
       <c r="D76">
-        <v>13.55883248141178</v>
+        <v>13.41675970401007</v>
       </c>
       <c r="E76">
-        <v>19.626</v>
+        <v>20.075</v>
       </c>
       <c r="F76">
-        <v>33.226</v>
+        <v>33.675</v>
       </c>
       <c r="G76">
         <v>0.5580000000000001</v>
@@ -7507,37 +7507,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M76">
-        <v>7.8346908</v>
+        <v>7.940564999999999</v>
       </c>
       <c r="N76">
-        <v>-4.954690799999999</v>
+        <v>-5.060564999999999</v>
       </c>
       <c r="O76">
-        <v>-1.2386727</v>
+        <v>-1.26514125</v>
       </c>
       <c r="P76">
-        <v>-3.716018099999999</v>
+        <v>-3.795423749999999</v>
       </c>
       <c r="Q76">
-        <v>-1.746018099999999</v>
+        <v>-1.825423749999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2162333206477982</v>
+        <v>0.2230506534737102</v>
       </c>
       <c r="T76">
-        <v>3.416107527855115</v>
+        <v>3.552751828969321</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09189896811243657</v>
+        <v>0.0906736485376041</v>
       </c>
       <c r="W76">
-        <v>0.2141302233190875</v>
+        <v>0.214419153674833</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3675958724497463</v>
+        <v>0.3626945941504164</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2165770286245522</v>
+        <v>0.2184770286245523</v>
       </c>
       <c r="C77">
-        <v>-19.70024029598993</v>
+        <v>-20.28836660033788</v>
       </c>
       <c r="D77">
-        <v>13.41675970401007</v>
+        <v>13.27763339966212</v>
       </c>
       <c r="E77">
-        <v>20.075</v>
+        <v>20.524</v>
       </c>
       <c r="F77">
-        <v>33.675</v>
+        <v>34.124</v>
       </c>
       <c r="G77">
         <v>0.5580000000000001</v>
@@ -7589,37 +7589,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M77">
-        <v>7.940564999999999</v>
+        <v>8.0464392</v>
       </c>
       <c r="N77">
-        <v>-5.060564999999999</v>
+        <v>-5.166439199999999</v>
       </c>
       <c r="O77">
-        <v>-1.26514125</v>
+        <v>-1.2916098</v>
       </c>
       <c r="P77">
-        <v>-3.795423749999999</v>
+        <v>-3.874829399999999</v>
       </c>
       <c r="Q77">
-        <v>-1.825423749999999</v>
+        <v>-1.904829399999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2230506534737102</v>
+        <v>0.2304360973684481</v>
       </c>
       <c r="T77">
-        <v>3.552751828969321</v>
+        <v>3.700783155176376</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0906736485376041</v>
+        <v>0.08948057421474087</v>
       </c>
       <c r="W77">
-        <v>0.214419153674833</v>
+        <v>0.2147004806001641</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3626945941504164</v>
+        <v>0.3579222968589635</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2184770286245523</v>
+        <v>0.2203770286245523</v>
       </c>
       <c r="C78">
-        <v>-20.28836660033788</v>
+        <v>-20.87363715205563</v>
       </c>
       <c r="D78">
-        <v>13.27763339966212</v>
+        <v>13.14136284794437</v>
       </c>
       <c r="E78">
-        <v>20.524</v>
+        <v>20.973</v>
       </c>
       <c r="F78">
-        <v>34.124</v>
+        <v>34.573</v>
       </c>
       <c r="G78">
         <v>0.5580000000000001</v>
@@ -7671,37 +7671,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M78">
-        <v>8.0464392</v>
+        <v>8.152313400000001</v>
       </c>
       <c r="N78">
-        <v>-5.166439199999999</v>
+        <v>-5.2723134</v>
       </c>
       <c r="O78">
-        <v>-1.2916098</v>
+        <v>-1.31807835</v>
       </c>
       <c r="P78">
-        <v>-3.874829399999999</v>
+        <v>-3.95423505</v>
       </c>
       <c r="Q78">
-        <v>-1.904829399999999</v>
+        <v>-1.98423505</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2304360973684481</v>
+        <v>0.2384637537757719</v>
       </c>
       <c r="T78">
-        <v>3.700783155176376</v>
+        <v>3.861686770618827</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08948057421474087</v>
+        <v>0.08831848883532865</v>
       </c>
       <c r="W78">
-        <v>0.2147004806001641</v>
+        <v>0.2149745003326295</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3579222968589635</v>
+        <v>0.3532739553413146</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2203770286245523</v>
+        <v>0.2222770286245523</v>
       </c>
       <c r="C79">
-        <v>-20.87363715205563</v>
+        <v>-21.45613898508674</v>
       </c>
       <c r="D79">
-        <v>13.14136284794437</v>
+        <v>13.00786101491326</v>
       </c>
       <c r="E79">
-        <v>20.973</v>
+        <v>21.422</v>
       </c>
       <c r="F79">
-        <v>34.573</v>
+        <v>35.022</v>
       </c>
       <c r="G79">
         <v>0.5580000000000001</v>
@@ -7753,37 +7753,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M79">
-        <v>8.152313400000001</v>
+        <v>8.258187599999999</v>
       </c>
       <c r="N79">
-        <v>-5.2723134</v>
+        <v>-5.378187599999999</v>
       </c>
       <c r="O79">
-        <v>-1.31807835</v>
+        <v>-1.3445469</v>
       </c>
       <c r="P79">
-        <v>-3.95423505</v>
+        <v>-4.033640699999999</v>
       </c>
       <c r="Q79">
-        <v>-1.98423505</v>
+        <v>-2.0636407</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2384637537757719</v>
+        <v>0.2472211971292161</v>
       </c>
       <c r="T79">
-        <v>3.861686770618827</v>
+        <v>4.037217987465137</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08831848883532865</v>
+        <v>0.08718620051692701</v>
       </c>
       <c r="W79">
-        <v>0.2149745003326295</v>
+        <v>0.2152414939181086</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3532739553413146</v>
+        <v>0.3487448020677081</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2222770286245523</v>
+        <v>0.2241770286245523</v>
       </c>
       <c r="C80">
-        <v>-21.45613898508674</v>
+        <v>-22.03595563226459</v>
       </c>
       <c r="D80">
-        <v>13.00786101491326</v>
+        <v>12.87704436773541</v>
       </c>
       <c r="E80">
-        <v>21.422</v>
+        <v>21.871</v>
       </c>
       <c r="F80">
-        <v>35.022</v>
+        <v>35.471</v>
       </c>
       <c r="G80">
         <v>0.5580000000000001</v>
@@ -7835,37 +7835,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M80">
-        <v>8.258187599999999</v>
+        <v>8.364061800000002</v>
       </c>
       <c r="N80">
-        <v>-5.378187599999999</v>
+        <v>-5.484061800000001</v>
       </c>
       <c r="O80">
-        <v>-1.3445469</v>
+        <v>-1.37101545</v>
       </c>
       <c r="P80">
-        <v>-4.033640699999999</v>
+        <v>-4.113046350000001</v>
       </c>
       <c r="Q80">
-        <v>-2.0636407</v>
+        <v>-2.143046350000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2472211971292161</v>
+        <v>0.2568126827067978</v>
       </c>
       <c r="T80">
-        <v>4.037217987465137</v>
+        <v>4.229466463058715</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08718620051692701</v>
+        <v>0.08608257772557348</v>
       </c>
       <c r="W80">
-        <v>0.2152414939181086</v>
+        <v>0.2155017281723098</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3487448020677081</v>
+        <v>0.3443303109022939</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2241770286245523</v>
+        <v>0.2260770286245523</v>
       </c>
       <c r="C81">
-        <v>-22.03595563226459</v>
+        <v>-22.61316729960825</v>
       </c>
       <c r="D81">
-        <v>12.87704436773541</v>
+        <v>12.74883270039175</v>
       </c>
       <c r="E81">
-        <v>21.871</v>
+        <v>22.32</v>
       </c>
       <c r="F81">
-        <v>35.471</v>
+        <v>35.92</v>
       </c>
       <c r="G81">
         <v>0.5580000000000001</v>
@@ -7917,37 +7917,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M81">
-        <v>8.364061800000002</v>
+        <v>8.469936000000001</v>
       </c>
       <c r="N81">
-        <v>-5.484061800000001</v>
+        <v>-5.589936</v>
       </c>
       <c r="O81">
-        <v>-1.37101545</v>
+        <v>-1.397484</v>
       </c>
       <c r="P81">
-        <v>-4.113046350000001</v>
+        <v>-4.192451999999999</v>
       </c>
       <c r="Q81">
-        <v>-2.143046350000001</v>
+        <v>-2.222452</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2568126827067978</v>
+        <v>0.2673633168421377</v>
       </c>
       <c r="T81">
-        <v>4.229466463058715</v>
+        <v>4.440939786211652</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08608257772557348</v>
+        <v>0.08500654550400383</v>
       </c>
       <c r="W81">
-        <v>0.2155017281723098</v>
+        <v>0.2157554565701559</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3443303109022939</v>
+        <v>0.3400261820160153</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2260770286245523</v>
+        <v>0.2279770286245523</v>
       </c>
       <c r="C82">
-        <v>-22.61316729960825</v>
+        <v>-23.18785103030865</v>
       </c>
       <c r="D82">
-        <v>12.74883270039175</v>
+        <v>12.62314896969135</v>
       </c>
       <c r="E82">
-        <v>22.32</v>
+        <v>22.769</v>
       </c>
       <c r="F82">
-        <v>35.92</v>
+        <v>36.369</v>
       </c>
       <c r="G82">
         <v>0.5580000000000001</v>
@@ -7999,37 +7999,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M82">
-        <v>8.469936000000001</v>
+        <v>8.575810200000001</v>
       </c>
       <c r="N82">
-        <v>-5.589936</v>
+        <v>-5.6958102</v>
       </c>
       <c r="O82">
-        <v>-1.397484</v>
+        <v>-1.42395255</v>
       </c>
       <c r="P82">
-        <v>-4.192451999999999</v>
+        <v>-4.27185765</v>
       </c>
       <c r="Q82">
-        <v>-2.222452</v>
+        <v>-2.301857650000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2673633168421377</v>
+        <v>0.2790245440443555</v>
       </c>
       <c r="T82">
-        <v>4.440939786211652</v>
+        <v>4.67467345917016</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08500654550400383</v>
+        <v>0.08395708197926303</v>
       </c>
       <c r="W82">
-        <v>0.2157554565701559</v>
+        <v>0.2160029200692898</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3400261820160153</v>
+        <v>0.3358283279170521</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2279770286245523</v>
+        <v>0.2298770286245523</v>
       </c>
       <c r="C83">
-        <v>-23.18785103030865</v>
+        <v>-23.76008085910954</v>
       </c>
       <c r="D83">
-        <v>12.62314896969135</v>
+        <v>12.49991914089047</v>
       </c>
       <c r="E83">
-        <v>22.769</v>
+        <v>23.218</v>
       </c>
       <c r="F83">
-        <v>36.369</v>
+        <v>36.818</v>
       </c>
       <c r="G83">
         <v>0.5580000000000001</v>
@@ -8081,37 +8081,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M83">
-        <v>8.575810200000001</v>
+        <v>8.681684400000002</v>
       </c>
       <c r="N83">
-        <v>-5.6958102</v>
+        <v>-5.801684400000001</v>
       </c>
       <c r="O83">
-        <v>-1.42395255</v>
+        <v>-1.4504211</v>
       </c>
       <c r="P83">
-        <v>-4.27185765</v>
+        <v>-4.351263300000001</v>
       </c>
       <c r="Q83">
-        <v>-2.301857650000001</v>
+        <v>-2.381263300000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2790245440443555</v>
+        <v>0.2919814631579308</v>
       </c>
       <c r="T83">
-        <v>4.67467345917016</v>
+        <v>4.934377540235168</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08395708197926303</v>
+        <v>0.08293321512585738</v>
       </c>
       <c r="W83">
-        <v>0.2160029200692898</v>
+        <v>0.2162443478733228</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3358283279170521</v>
+        <v>0.3317328605034295</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2298770286245523</v>
+        <v>0.2317770286245523</v>
       </c>
       <c r="C84">
-        <v>-23.76008085910954</v>
+        <v>-24.32992795773326</v>
       </c>
       <c r="D84">
-        <v>12.49991914089047</v>
+        <v>12.37907204226674</v>
       </c>
       <c r="E84">
-        <v>23.218</v>
+        <v>23.667</v>
       </c>
       <c r="F84">
-        <v>36.818</v>
+        <v>37.267</v>
       </c>
       <c r="G84">
         <v>0.5580000000000001</v>
@@ -8163,37 +8163,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M84">
-        <v>8.681684400000002</v>
+        <v>8.787558600000001</v>
       </c>
       <c r="N84">
-        <v>-5.801684400000001</v>
+        <v>-5.9075586</v>
       </c>
       <c r="O84">
-        <v>-1.4504211</v>
+        <v>-1.47688965</v>
       </c>
       <c r="P84">
-        <v>-4.351263300000001</v>
+        <v>-4.430668949999999</v>
       </c>
       <c r="Q84">
-        <v>-2.381263300000001</v>
+        <v>-2.46066895</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2919814631579308</v>
+        <v>0.3064627256966327</v>
       </c>
       <c r="T84">
-        <v>4.934377540235168</v>
+        <v>5.224635042601943</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08293321512585738</v>
+        <v>0.08193401976289526</v>
       </c>
       <c r="W84">
-        <v>0.2162443478733228</v>
+        <v>0.2164799581399093</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3317328605034295</v>
+        <v>0.327736079051581</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2317770286245523</v>
+        <v>0.2336770286245523</v>
       </c>
       <c r="C85">
-        <v>-24.32992795773326</v>
+        <v>-24.89746077195166</v>
       </c>
       <c r="D85">
-        <v>12.37907204226674</v>
+        <v>12.26053922804835</v>
       </c>
       <c r="E85">
-        <v>23.667</v>
+        <v>24.116</v>
       </c>
       <c r="F85">
-        <v>37.267</v>
+        <v>37.716</v>
       </c>
       <c r="G85">
         <v>0.5580000000000001</v>
@@ -8245,37 +8245,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M85">
-        <v>8.787558600000001</v>
+        <v>8.893432800000001</v>
       </c>
       <c r="N85">
-        <v>-5.9075586</v>
+        <v>-6.0134328</v>
       </c>
       <c r="O85">
-        <v>-1.47688965</v>
+        <v>-1.5033582</v>
       </c>
       <c r="P85">
-        <v>-4.430668949999999</v>
+        <v>-4.5100746</v>
       </c>
       <c r="Q85">
-        <v>-2.46066895</v>
+        <v>-2.540074600000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3064627256966327</v>
+        <v>0.3227541460526723</v>
       </c>
       <c r="T85">
-        <v>5.224635042601943</v>
+        <v>5.551174732764566</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08193401976289526</v>
+        <v>0.08095861476571792</v>
       </c>
       <c r="W85">
-        <v>0.2164799581399093</v>
+        <v>0.2167099586382437</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.327736079051581</v>
+        <v>0.3238344590628717</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2336770286245523</v>
+        <v>0.2355770286245523</v>
       </c>
       <c r="C86">
-        <v>-24.89746077195164</v>
+        <v>-25.46274515085658</v>
       </c>
       <c r="D86">
-        <v>12.26053922804835</v>
+        <v>12.14425484914342</v>
       </c>
       <c r="E86">
-        <v>24.11599999999999</v>
+        <v>24.565</v>
       </c>
       <c r="F86">
-        <v>37.71599999999999</v>
+        <v>38.165</v>
       </c>
       <c r="G86">
         <v>0.5580000000000001</v>
@@ -8327,37 +8327,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M86">
-        <v>8.893432799999999</v>
+        <v>8.999307</v>
       </c>
       <c r="N86">
-        <v>-6.013432799999999</v>
+        <v>-6.119306999999999</v>
       </c>
       <c r="O86">
-        <v>-1.5033582</v>
+        <v>-1.52982675</v>
       </c>
       <c r="P86">
-        <v>-4.510074599999999</v>
+        <v>-4.589480249999999</v>
       </c>
       <c r="Q86">
-        <v>-2.5400746</v>
+        <v>-2.61948025</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3227541460526721</v>
+        <v>0.3412177557895169</v>
       </c>
       <c r="T86">
-        <v>5.551174732764562</v>
+        <v>5.921253048282201</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08095861476571795</v>
+        <v>0.08000616047435655</v>
       </c>
       <c r="W86">
-        <v>0.2167099586382437</v>
+        <v>0.2169345473601468</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3238344590628718</v>
+        <v>0.3200246418974262</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2355770286245523</v>
+        <v>0.2374770286245523</v>
       </c>
       <c r="C87">
-        <v>-25.46274515085658</v>
+        <v>-26.02584446884334</v>
       </c>
       <c r="D87">
-        <v>12.14425484914342</v>
+        <v>12.03015553115666</v>
       </c>
       <c r="E87">
-        <v>24.565</v>
+        <v>25.014</v>
       </c>
       <c r="F87">
-        <v>38.165</v>
+        <v>38.614</v>
       </c>
       <c r="G87">
         <v>0.5580000000000001</v>
@@ -8409,37 +8409,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M87">
-        <v>8.999307</v>
+        <v>9.105181200000001</v>
       </c>
       <c r="N87">
-        <v>-6.119306999999999</v>
+        <v>-6.2251812</v>
       </c>
       <c r="O87">
-        <v>-1.52982675</v>
+        <v>-1.5562953</v>
       </c>
       <c r="P87">
-        <v>-4.589480249999999</v>
+        <v>-4.668885899999999</v>
       </c>
       <c r="Q87">
-        <v>-2.61948025</v>
+        <v>-2.6988859</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3412177557895169</v>
+        <v>0.3623190240601967</v>
       </c>
       <c r="T87">
-        <v>5.921253048282201</v>
+        <v>6.344199694588072</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08000616047435655</v>
+        <v>0.07907585628279426</v>
       </c>
       <c r="W87">
-        <v>0.2169345473601468</v>
+        <v>0.2171539130885171</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3200246418974262</v>
+        <v>0.316303425131177</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2374770286245523</v>
+        <v>0.2393770286245522</v>
       </c>
       <c r="C88">
-        <v>-26.02584446884334</v>
+        <v>-26.58681974078156</v>
       </c>
       <c r="D88">
-        <v>12.03015553115666</v>
+        <v>11.91818025921843</v>
       </c>
       <c r="E88">
-        <v>25.014</v>
+        <v>25.46299999999999</v>
       </c>
       <c r="F88">
-        <v>38.614</v>
+        <v>39.063</v>
       </c>
       <c r="G88">
         <v>0.5580000000000001</v>
@@ -8491,37 +8491,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M88">
-        <v>9.105181200000001</v>
+        <v>9.211055399999999</v>
       </c>
       <c r="N88">
-        <v>-6.2251812</v>
+        <v>-6.331055399999999</v>
       </c>
       <c r="O88">
-        <v>-1.5562953</v>
+        <v>-1.58276385</v>
       </c>
       <c r="P88">
-        <v>-4.668885899999999</v>
+        <v>-4.748291549999999</v>
       </c>
       <c r="Q88">
-        <v>-2.6988859</v>
+        <v>-2.77829155</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3623190240601967</v>
+        <v>0.3866666412955964</v>
       </c>
       <c r="T88">
-        <v>6.344199694588072</v>
+        <v>6.832215055710231</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07907585628279426</v>
+        <v>0.07816693839448628</v>
       </c>
       <c r="W88">
-        <v>0.2171539130885171</v>
+        <v>0.2173682359265801</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.316303425131177</v>
+        <v>0.3126677535779452</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2393770286245522</v>
+        <v>0.2412770286245523</v>
       </c>
       <c r="C89">
-        <v>-26.58681974078156</v>
+        <v>-27.14572973081353</v>
       </c>
       <c r="D89">
-        <v>11.91818025921843</v>
+        <v>11.80827026918647</v>
       </c>
       <c r="E89">
-        <v>25.46299999999999</v>
+        <v>25.912</v>
       </c>
       <c r="F89">
-        <v>39.063</v>
+        <v>39.512</v>
       </c>
       <c r="G89">
         <v>0.5580000000000001</v>
@@ -8573,37 +8573,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M89">
-        <v>9.211055399999999</v>
+        <v>9.3169296</v>
       </c>
       <c r="N89">
-        <v>-6.331055399999999</v>
+        <v>-6.436929599999999</v>
       </c>
       <c r="O89">
-        <v>-1.58276385</v>
+        <v>-1.6092324</v>
       </c>
       <c r="P89">
-        <v>-4.748291549999999</v>
+        <v>-4.827697199999999</v>
       </c>
       <c r="Q89">
-        <v>-2.77829155</v>
+        <v>-2.8576972</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3866666412955964</v>
+        <v>0.4150721947368962</v>
       </c>
       <c r="T89">
-        <v>6.832215055710231</v>
+        <v>7.401566310352751</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07816693839448628</v>
+        <v>0.07727867773091257</v>
       </c>
       <c r="W89">
-        <v>0.2173682359265801</v>
+        <v>0.2175776877910508</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3126677535779452</v>
+        <v>0.3091147109236503</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2412770286245523</v>
+        <v>0.2431770286245523</v>
       </c>
       <c r="C90">
-        <v>-27.14572973081353</v>
+        <v>-27.70263105518726</v>
       </c>
       <c r="D90">
-        <v>11.80827026918647</v>
+        <v>11.70036894481273</v>
       </c>
       <c r="E90">
-        <v>25.912</v>
+        <v>26.361</v>
       </c>
       <c r="F90">
-        <v>39.512</v>
+        <v>39.961</v>
       </c>
       <c r="G90">
         <v>0.5580000000000001</v>
@@ -8655,37 +8655,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M90">
-        <v>9.3169296</v>
+        <v>9.422803800000001</v>
       </c>
       <c r="N90">
-        <v>-6.436929599999999</v>
+        <v>-6.5428038</v>
       </c>
       <c r="O90">
-        <v>-1.6092324</v>
+        <v>-1.63570095</v>
       </c>
       <c r="P90">
-        <v>-4.827697199999999</v>
+        <v>-4.907102849999999</v>
       </c>
       <c r="Q90">
-        <v>-2.8576972</v>
+        <v>-2.93710285</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4150721947368962</v>
+        <v>0.4486423942584322</v>
       </c>
       <c r="T90">
-        <v>7.401566310352751</v>
+        <v>8.074435974930275</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07727867773091257</v>
+        <v>0.07641037798112703</v>
       </c>
       <c r="W90">
-        <v>0.2175776877910508</v>
+        <v>0.2177824328720503</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3091147109236503</v>
+        <v>0.3056415119245082</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2431770286245523</v>
+        <v>0.2450770286245523</v>
       </c>
       <c r="C91">
-        <v>-27.70263105518726</v>
+        <v>-28.25757827950291</v>
       </c>
       <c r="D91">
-        <v>11.70036894481273</v>
+        <v>11.59442172049709</v>
       </c>
       <c r="E91">
-        <v>26.361</v>
+        <v>26.81</v>
       </c>
       <c r="F91">
-        <v>39.961</v>
+        <v>40.41</v>
       </c>
       <c r="G91">
         <v>0.5580000000000001</v>
@@ -8737,37 +8737,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M91">
-        <v>9.422803800000001</v>
+        <v>9.528677999999999</v>
       </c>
       <c r="N91">
-        <v>-6.5428038</v>
+        <v>-6.648677999999999</v>
       </c>
       <c r="O91">
-        <v>-1.63570095</v>
+        <v>-1.6621695</v>
       </c>
       <c r="P91">
-        <v>-4.907102849999999</v>
+        <v>-4.986508499999999</v>
       </c>
       <c r="Q91">
-        <v>-2.93710285</v>
+        <v>-3.0165085</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4486423942584322</v>
+        <v>0.4889266336842755</v>
       </c>
       <c r="T91">
-        <v>8.074435974930275</v>
+        <v>8.881879572423303</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07641037798112703</v>
+        <v>0.07556137378133675</v>
       </c>
       <c r="W91">
-        <v>0.2177824328720503</v>
+        <v>0.2179826280623608</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3056415119245082</v>
+        <v>0.3022454951253469</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2450770286245523</v>
+        <v>0.2469770286245523</v>
       </c>
       <c r="C92">
-        <v>-28.25757827950291</v>
+        <v>-28.81062401072294</v>
       </c>
       <c r="D92">
-        <v>11.59442172049709</v>
+        <v>11.49037598927707</v>
       </c>
       <c r="E92">
-        <v>26.81</v>
+        <v>27.259</v>
       </c>
       <c r="F92">
-        <v>40.41</v>
+        <v>40.859</v>
       </c>
       <c r="G92">
         <v>0.5580000000000001</v>
@@ -8819,37 +8819,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M92">
-        <v>9.528677999999999</v>
+        <v>9.634552200000002</v>
       </c>
       <c r="N92">
-        <v>-6.648677999999999</v>
+        <v>-6.754552200000001</v>
       </c>
       <c r="O92">
-        <v>-1.6621695</v>
+        <v>-1.68863805</v>
       </c>
       <c r="P92">
-        <v>-4.986508499999999</v>
+        <v>-5.065914150000001</v>
       </c>
       <c r="Q92">
-        <v>-3.0165085</v>
+        <v>-3.095914150000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4889266336842755</v>
+        <v>0.5381629263158616</v>
       </c>
       <c r="T92">
-        <v>8.881879572423303</v>
+        <v>9.868755080470336</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07556137378133675</v>
+        <v>0.07473102901450884</v>
       </c>
       <c r="W92">
-        <v>0.2179826280623608</v>
+        <v>0.2181784233583788</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3022454951253469</v>
+        <v>0.2989241160580354</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2469770286245523</v>
+        <v>0.2488770286245523</v>
       </c>
       <c r="C93">
-        <v>-28.81062401072294</v>
+        <v>-29.36181898427238</v>
       </c>
       <c r="D93">
-        <v>11.49037598927707</v>
+        <v>11.38818101572762</v>
       </c>
       <c r="E93">
-        <v>27.259</v>
+        <v>27.708</v>
       </c>
       <c r="F93">
-        <v>40.859</v>
+        <v>41.308</v>
       </c>
       <c r="G93">
         <v>0.5580000000000001</v>
@@ -8901,37 +8901,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M93">
-        <v>9.634552200000002</v>
+        <v>9.7404264</v>
       </c>
       <c r="N93">
-        <v>-6.754552200000001</v>
+        <v>-6.8604264</v>
       </c>
       <c r="O93">
-        <v>-1.68863805</v>
+        <v>-1.7151066</v>
       </c>
       <c r="P93">
-        <v>-5.065914150000001</v>
+        <v>-5.145319799999999</v>
       </c>
       <c r="Q93">
-        <v>-3.095914150000001</v>
+        <v>-3.1753198</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5381629263158616</v>
+        <v>0.5997082921053446</v>
       </c>
       <c r="T93">
-        <v>9.868755080470336</v>
+        <v>11.10234946552913</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07473102901450884</v>
+        <v>0.07391873522087289</v>
       </c>
       <c r="W93">
-        <v>0.2181784233583788</v>
+        <v>0.2183699622349182</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2989241160580354</v>
+        <v>0.2956749408834916</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2488770286245523</v>
+        <v>0.2507770286245523</v>
       </c>
       <c r="C94">
-        <v>-29.36181898427238</v>
+        <v>-29.91121214653212</v>
       </c>
       <c r="D94">
-        <v>11.38818101572762</v>
+        <v>11.28778785346788</v>
       </c>
       <c r="E94">
-        <v>27.708</v>
+        <v>28.157</v>
       </c>
       <c r="F94">
-        <v>41.308</v>
+        <v>41.757</v>
       </c>
       <c r="G94">
         <v>0.5580000000000001</v>
@@ -8983,37 +8983,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M94">
-        <v>9.7404264</v>
+        <v>9.846300599999999</v>
       </c>
       <c r="N94">
-        <v>-6.8604264</v>
+        <v>-6.966300599999999</v>
       </c>
       <c r="O94">
-        <v>-1.7151066</v>
+        <v>-1.74157515</v>
       </c>
       <c r="P94">
-        <v>-5.145319799999999</v>
+        <v>-5.224725449999999</v>
       </c>
       <c r="Q94">
-        <v>-3.1753198</v>
+        <v>-3.25472545</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5997082921053446</v>
+        <v>0.6788380481203938</v>
       </c>
       <c r="T94">
-        <v>11.10234946552913</v>
+        <v>12.68839938917615</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07391873522087289</v>
+        <v>0.07312391011097104</v>
       </c>
       <c r="W94">
-        <v>0.2183699622349182</v>
+        <v>0.218557381995833</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2956749408834916</v>
+        <v>0.2924956404438842</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2507770286245523</v>
+        <v>0.2526770286245523</v>
       </c>
       <c r="C95">
-        <v>-29.91121214653212</v>
+        <v>-30.45885073300684</v>
       </c>
       <c r="D95">
-        <v>11.28778785346788</v>
+        <v>11.18914926699316</v>
       </c>
       <c r="E95">
-        <v>28.157</v>
+        <v>28.606</v>
       </c>
       <c r="F95">
-        <v>41.757</v>
+        <v>42.206</v>
       </c>
       <c r="G95">
         <v>0.5580000000000001</v>
@@ -9065,37 +9065,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M95">
-        <v>9.846300599999999</v>
+        <v>9.952174800000002</v>
       </c>
       <c r="N95">
-        <v>-6.966300599999999</v>
+        <v>-7.072174800000001</v>
       </c>
       <c r="O95">
-        <v>-1.74157515</v>
+        <v>-1.7680437</v>
       </c>
       <c r="P95">
-        <v>-5.224725449999999</v>
+        <v>-5.304131100000001</v>
       </c>
       <c r="Q95">
-        <v>-3.25472545</v>
+        <v>-3.334131100000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6788380481203938</v>
+        <v>0.784344389473793</v>
       </c>
       <c r="T95">
-        <v>12.68839938917615</v>
+        <v>14.80313262070552</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07312391011097104</v>
+        <v>0.07234599617362027</v>
       </c>
       <c r="W95">
-        <v>0.218557381995833</v>
+        <v>0.2187408141022603</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2924956404438842</v>
+        <v>0.2893839846944811</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2526770286245523</v>
+        <v>0.2545770286245523</v>
       </c>
       <c r="C96">
-        <v>-30.45885073300684</v>
+        <v>-31.00478034243016</v>
       </c>
       <c r="D96">
-        <v>11.18914926699316</v>
+        <v>11.09221965756984</v>
       </c>
       <c r="E96">
-        <v>28.606</v>
+        <v>29.055</v>
       </c>
       <c r="F96">
-        <v>42.206</v>
+        <v>42.655</v>
       </c>
       <c r="G96">
         <v>0.5580000000000001</v>
@@ -9147,37 +9147,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M96">
-        <v>9.952174800000002</v>
+        <v>10.058049</v>
       </c>
       <c r="N96">
-        <v>-7.072174800000001</v>
+        <v>-7.178049</v>
       </c>
       <c r="O96">
-        <v>-1.7680437</v>
+        <v>-1.79451225</v>
       </c>
       <c r="P96">
-        <v>-5.304131100000001</v>
+        <v>-5.383536749999999</v>
       </c>
       <c r="Q96">
-        <v>-3.334131100000001</v>
+        <v>-3.41353675</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.784344389473793</v>
+        <v>0.932053267368552</v>
       </c>
       <c r="T96">
-        <v>14.80313262070552</v>
+        <v>17.76375914484663</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07234599617362027</v>
+        <v>0.0715844593717927</v>
       </c>
       <c r="W96">
-        <v>0.2187408141022603</v>
+        <v>0.2189203844801313</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2893839846944811</v>
+        <v>0.2863378374871708</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2545770286245523</v>
+        <v>0.2564770286245522</v>
       </c>
       <c r="C97">
-        <v>-31.00478034243016</v>
+        <v>-31.54904500705096</v>
       </c>
       <c r="D97">
-        <v>11.09221965756984</v>
+        <v>10.99695499294903</v>
       </c>
       <c r="E97">
-        <v>29.055</v>
+        <v>29.504</v>
       </c>
       <c r="F97">
-        <v>42.655</v>
+        <v>43.104</v>
       </c>
       <c r="G97">
         <v>0.5580000000000001</v>
@@ -9229,37 +9229,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M97">
-        <v>10.058049</v>
+        <v>10.1639232</v>
       </c>
       <c r="N97">
-        <v>-7.178049</v>
+        <v>-7.2839232</v>
       </c>
       <c r="O97">
-        <v>-1.79451225</v>
+        <v>-1.8209808</v>
       </c>
       <c r="P97">
-        <v>-5.383536749999999</v>
+        <v>-5.4629424</v>
       </c>
       <c r="Q97">
-        <v>-3.41353675</v>
+        <v>-3.4929424</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.932053267368552</v>
+        <v>1.15361658421069</v>
       </c>
       <c r="T97">
-        <v>17.76375914484663</v>
+        <v>22.20469893105829</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0715844593717927</v>
+        <v>0.07083878792000319</v>
       </c>
       <c r="W97">
-        <v>0.2189203844801313</v>
+        <v>0.2190962138084633</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2863378374871708</v>
+        <v>0.2833551516800128</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2564770286245522</v>
+        <v>0.2583770286245523</v>
       </c>
       <c r="C98">
-        <v>-31.54904500705096</v>
+        <v>-32.09168725932885</v>
       </c>
       <c r="D98">
-        <v>10.99695499294903</v>
+        <v>10.90331274067115</v>
       </c>
       <c r="E98">
-        <v>29.504</v>
+        <v>29.953</v>
       </c>
       <c r="F98">
-        <v>43.104</v>
+        <v>43.553</v>
       </c>
       <c r="G98">
         <v>0.5580000000000001</v>
@@ -9311,37 +9311,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M98">
-        <v>10.1639232</v>
+        <v>10.2697974</v>
       </c>
       <c r="N98">
-        <v>-7.2839232</v>
+        <v>-7.389797399999999</v>
       </c>
       <c r="O98">
-        <v>-1.8209808</v>
+        <v>-1.84744935</v>
       </c>
       <c r="P98">
-        <v>-5.4629424</v>
+        <v>-5.542348049999999</v>
       </c>
       <c r="Q98">
-        <v>-3.4929424</v>
+        <v>-3.57234805</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.153616584210688</v>
+        <v>1.522888778947584</v>
       </c>
       <c r="T98">
-        <v>22.20469893105823</v>
+        <v>29.60626524141098</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07083878792000319</v>
+        <v>0.07010849113732275</v>
       </c>
       <c r="W98">
-        <v>0.2190962138084633</v>
+        <v>0.2192684177898193</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2833551516800128</v>
+        <v>0.280433964549291</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2583770286245523</v>
+        <v>0.2602770286245523</v>
       </c>
       <c r="C99">
-        <v>-32.09168725932885</v>
+        <v>-32.63274819525058</v>
       </c>
       <c r="D99">
-        <v>10.90331274067115</v>
+        <v>10.81125180474941</v>
       </c>
       <c r="E99">
-        <v>29.953</v>
+        <v>30.40199999999999</v>
       </c>
       <c r="F99">
-        <v>43.553</v>
+        <v>44.002</v>
       </c>
       <c r="G99">
         <v>0.5580000000000001</v>
@@ -9393,37 +9393,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M99">
-        <v>10.2697974</v>
+        <v>10.3756716</v>
       </c>
       <c r="N99">
-        <v>-7.389797399999999</v>
+        <v>-7.495671599999998</v>
       </c>
       <c r="O99">
-        <v>-1.84744935</v>
+        <v>-1.873917899999999</v>
       </c>
       <c r="P99">
-        <v>-5.542348049999999</v>
+        <v>-5.621753699999998</v>
       </c>
       <c r="Q99">
-        <v>-3.57234805</v>
+        <v>-3.651753699999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.522888778947584</v>
+        <v>2.261433168421375</v>
       </c>
       <c r="T99">
-        <v>29.60626524141098</v>
+        <v>44.40939786211647</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07010849113732275</v>
+        <v>0.06939309837061539</v>
       </c>
       <c r="W99">
-        <v>0.2192684177898193</v>
+        <v>0.2194371074042089</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.280433964549291</v>
+        <v>0.2775723934824615</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2602770286245523</v>
+        <v>0.2621770286245523</v>
       </c>
       <c r="C100">
-        <v>-32.63274819525058</v>
+        <v>-33.17226753446592</v>
       </c>
       <c r="D100">
-        <v>10.81125180474941</v>
+        <v>10.72073246553409</v>
       </c>
       <c r="E100">
-        <v>30.40199999999999</v>
+        <v>30.851</v>
       </c>
       <c r="F100">
-        <v>44.002</v>
+        <v>44.451</v>
       </c>
       <c r="G100">
         <v>0.5580000000000001</v>
@@ -9475,37 +9475,37 @@
         <v>2.880000000000001</v>
       </c>
       <c r="M100">
-        <v>10.3756716</v>
+        <v>10.4815458</v>
       </c>
       <c r="N100">
-        <v>-7.495671599999998</v>
+        <v>-7.6015458</v>
       </c>
       <c r="O100">
-        <v>-1.873917899999999</v>
+        <v>-1.90038645</v>
       </c>
       <c r="P100">
-        <v>-5.621753699999998</v>
+        <v>-5.70115935</v>
       </c>
       <c r="Q100">
-        <v>-3.651753699999999</v>
+        <v>-3.73115935</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.261433168421375</v>
+        <v>4.47706633684275</v>
       </c>
       <c r="T100">
-        <v>44.40939786211647</v>
+        <v>88.81879572423293</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06939309837061539</v>
+        <v>0.06869215798303339</v>
       </c>
       <c r="W100">
-        <v>0.2194371074042089</v>
+        <v>0.2196023891476007</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2775723934824615</v>
+        <v>0.2747686319321335</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2621770286245523</v>
-      </c>
-      <c r="C101">
-        <v>-33.17226753446592</v>
-      </c>
-      <c r="D101">
-        <v>10.72073246553409</v>
-      </c>
-      <c r="E101">
-        <v>30.851</v>
-      </c>
-      <c r="F101">
-        <v>44.451</v>
-      </c>
-      <c r="G101">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="H101">
-        <v>31.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.850000000000001</v>
-      </c>
-      <c r="K101">
-        <v>1.97</v>
-      </c>
-      <c r="L101">
-        <v>2.880000000000001</v>
-      </c>
-      <c r="M101">
-        <v>10.4815458</v>
-      </c>
-      <c r="N101">
-        <v>-7.6015458</v>
-      </c>
-      <c r="O101">
-        <v>-1.90038645</v>
-      </c>
-      <c r="P101">
-        <v>-5.70115935</v>
-      </c>
-      <c r="Q101">
-        <v>-3.73115935</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.47706633684275</v>
-      </c>
-      <c r="T101">
-        <v>88.81879572423293</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06869215798303339</v>
-      </c>
-      <c r="W101">
-        <v>0.2196023891476007</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2747686319321335</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
